--- a/api/clv3/xlsx/en/ReportingOrganisation.xlsx
+++ b/api/clv3/xlsx/en/ReportingOrganisation.xlsx
@@ -25,15 +25,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:organisation-type-code</t>
+  </si>
+  <si>
+    <t>codeforiati:hq-country-or-region</t>
+  </si>
+  <si>
     <t>codeforiati:organisation-type</t>
   </si>
   <si>
-    <t>codeforiati:hq-country-or-region</t>
-  </si>
-  <si>
-    <t>codeforiati:organisation-type-code</t>
-  </si>
-  <si>
     <t>AU-5</t>
   </si>
   <si>
@@ -43,45 +43,45 @@
     <t>active</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
     <t>Government</t>
   </si>
   <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>44000</t>
   </si>
   <si>
     <t>The World Bank</t>
   </si>
   <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>(No country assigned)</t>
+  </si>
+  <si>
     <t>Multilateral</t>
   </si>
   <si>
-    <t>(No country assigned)</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>US-EIN-941655673</t>
   </si>
   <si>
     <t>The William and Flora Hewlett Foundation</t>
   </si>
   <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
     <t>Foundation</t>
   </si>
   <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>41AAA</t>
   </si>
   <si>
@@ -94,27 +94,27 @@
     <t>Frontline AIDS</t>
   </si>
   <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
     <t>International NGO</t>
   </si>
   <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>XI-IATI-EC_DEVCO</t>
   </si>
   <si>
     <t>European Commission - Directorate-General for International Cooperation and Development</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>Other Public Sector</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>SE-0</t>
   </si>
   <si>
@@ -229,12 +229,12 @@
     <t>Gavi, the vaccine alliance</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>Public Private Partnership</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>US-EIN-300108263</t>
   </si>
   <si>
@@ -277,15 +277,15 @@
     <t>Young Innovations Pvt. Ltd</t>
   </si>
   <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>Nepal</t>
+  </si>
+  <si>
     <t>Academic, Training and Research</t>
   </si>
   <si>
-    <t>Nepal</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
     <t>GB-CHC-327421</t>
   </si>
   <si>
@@ -391,12 +391,12 @@
     <t>ICA:UK</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>National NGO</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>GB-CHC-298316</t>
   </si>
   <si>
@@ -619,15 +619,15 @@
     <t>Southern African Catholic Bishops' Conference Aids Office</t>
   </si>
   <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
     <t>Regional NGO</t>
   </si>
   <si>
-    <t>South Africa</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
     <t>30001</t>
   </si>
   <si>
@@ -808,10 +808,10 @@
     <t>Triple Line</t>
   </si>
   <si>
+    <t>70</t>
+  </si>
+  <si>
     <t>Private Sector</t>
-  </si>
-  <si>
-    <t>70</t>
   </si>
   <si>
     <t>GB-CHC-1058991</t>

--- a/api/clv3/xlsx/en/ReportingOrganisation.xlsx
+++ b/api/clv3/xlsx/en/ReportingOrganisation.xlsx
@@ -25,12 +25,12 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:organisation-type</t>
+  </si>
+  <si>
     <t>codeforiati:organisation-type-code</t>
   </si>
   <si>
-    <t>codeforiati:organisation-type</t>
-  </si>
-  <si>
     <t>codeforiati:hq-country-or-region</t>
   </si>
   <si>
@@ -43,12 +43,12 @@
     <t>active</t>
   </si>
   <si>
+    <t>Government</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
-    <t>Government</t>
-  </si>
-  <si>
     <t>Australia</t>
   </si>
   <si>
@@ -58,12 +58,12 @@
     <t>The World Bank</t>
   </si>
   <si>
+    <t>Multilateral</t>
+  </si>
+  <si>
     <t>40</t>
   </si>
   <si>
-    <t>Multilateral</t>
-  </si>
-  <si>
     <t>(No country assigned)</t>
   </si>
   <si>
@@ -73,12 +73,12 @@
     <t>The William and Flora Hewlett Foundation</t>
   </si>
   <si>
+    <t>Foundation</t>
+  </si>
+  <si>
     <t>60</t>
   </si>
   <si>
-    <t>Foundation</t>
-  </si>
-  <si>
     <t>United States</t>
   </si>
   <si>
@@ -94,12 +94,12 @@
     <t>Frontline AIDS</t>
   </si>
   <si>
+    <t>International NGO</t>
+  </si>
+  <si>
     <t>21</t>
   </si>
   <si>
-    <t>International NGO</t>
-  </si>
-  <si>
     <t>United Kingdom</t>
   </si>
   <si>
@@ -109,12 +109,12 @@
     <t>European Commission - Directorate-General for International Cooperation and Development</t>
   </si>
   <si>
+    <t>Other Public Sector</t>
+  </si>
+  <si>
     <t>15</t>
   </si>
   <si>
-    <t>Other Public Sector</t>
-  </si>
-  <si>
     <t>SE-0</t>
   </si>
   <si>
@@ -229,12 +229,12 @@
     <t>Gavi, the vaccine alliance</t>
   </si>
   <si>
+    <t>Public Private Partnership</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
-    <t>Public Private Partnership</t>
-  </si>
-  <si>
     <t>US-EIN-300108263</t>
   </si>
   <si>
@@ -277,12 +277,12 @@
     <t>Young Innovations Pvt. Ltd</t>
   </si>
   <si>
+    <t>Academic, Training and Research</t>
+  </si>
+  <si>
     <t>80</t>
   </si>
   <si>
-    <t>Academic, Training and Research</t>
-  </si>
-  <si>
     <t>Nepal</t>
   </si>
   <si>
@@ -391,12 +391,12 @@
     <t>ICA:UK</t>
   </si>
   <si>
+    <t>National NGO</t>
+  </si>
+  <si>
     <t>22</t>
   </si>
   <si>
-    <t>National NGO</t>
-  </si>
-  <si>
     <t>GB-CHC-298316</t>
   </si>
   <si>
@@ -619,12 +619,12 @@
     <t>Southern African Catholic Bishops' Conference Aids Office</t>
   </si>
   <si>
+    <t>Regional NGO</t>
+  </si>
+  <si>
     <t>23</t>
   </si>
   <si>
-    <t>Regional NGO</t>
-  </si>
-  <si>
     <t>South Africa</t>
   </si>
   <si>
@@ -808,10 +808,10 @@
     <t>Triple Line</t>
   </si>
   <si>
+    <t>Private Sector</t>
+  </si>
+  <si>
     <t>70</t>
-  </si>
-  <si>
-    <t>Private Sector</t>
   </si>
   <si>
     <t>GB-CHC-1058991</t>

--- a/api/clv3/xlsx/en/ReportingOrganisation.xlsx
+++ b/api/clv3/xlsx/en/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7440" uniqueCount="2586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7452" uniqueCount="2590">
   <si>
     <t>code</t>
   </si>
@@ -5911,7 +5911,7 @@
     <t>DK-CVR-12006004</t>
   </si>
   <si>
-    <t>Dansk MissionrÃ¥ds Udviklingsafdeling</t>
+    <t>Center for Church-Based Development</t>
   </si>
   <si>
     <t>XI-GRID-grid.9829.a</t>
@@ -7657,6 +7657,12 @@
     <t>University of Cape Town</t>
   </si>
   <si>
+    <t>XI-IATI-KHF</t>
+  </si>
+  <si>
+    <t>King Hussein Foundation</t>
+  </si>
+  <si>
     <t>GB-CHC-1158838</t>
   </si>
   <si>
@@ -7757,6 +7763,12 @@
   </si>
   <si>
     <t>CGIAR</t>
+  </si>
+  <si>
+    <t>UG-RSB-197310</t>
+  </si>
+  <si>
+    <t>Financial Sector Deepening Uganda</t>
   </si>
   <si>
     <t>ZM-PCR-12015013762</t>
@@ -8103,7 +8115,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1240"/>
+  <dimension ref="A1:F1242"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -32537,13 +32549,13 @@
         <v>8</v>
       </c>
       <c r="D1222" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E1222" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F1222" t="s">
-        <v>28</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="1223" spans="1:6">
@@ -32563,7 +32575,7 @@
         <v>27</v>
       </c>
       <c r="F1223" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1224" spans="1:6">
@@ -32583,7 +32595,7 @@
         <v>27</v>
       </c>
       <c r="F1224" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1225" spans="1:6">
@@ -32597,13 +32609,13 @@
         <v>8</v>
       </c>
       <c r="D1225" t="s">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="E1225" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="F1225" t="s">
-        <v>2252</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1226" spans="1:6">
@@ -32623,7 +32635,7 @@
         <v>126</v>
       </c>
       <c r="F1226" t="s">
-        <v>2519</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1227" spans="1:6">
@@ -32637,13 +32649,13 @@
         <v>8</v>
       </c>
       <c r="D1227" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="E1227" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="F1227" t="s">
-        <v>28</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="1228" spans="1:6">
@@ -32657,13 +32669,13 @@
         <v>8</v>
       </c>
       <c r="D1228" t="s">
-        <v>264</v>
+        <v>26</v>
       </c>
       <c r="E1228" t="s">
-        <v>265</v>
+        <v>27</v>
       </c>
       <c r="F1228" t="s">
-        <v>1366</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1229" spans="1:6">
@@ -32677,13 +32689,13 @@
         <v>8</v>
       </c>
       <c r="D1229" t="s">
-        <v>125</v>
+        <v>264</v>
       </c>
       <c r="E1229" t="s">
-        <v>126</v>
+        <v>265</v>
       </c>
       <c r="F1229" t="s">
-        <v>797</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="1230" spans="1:6">
@@ -32703,7 +32715,7 @@
         <v>126</v>
       </c>
       <c r="F1230" t="s">
-        <v>21</v>
+        <v>797</v>
       </c>
     </row>
     <row r="1231" spans="1:6">
@@ -32717,13 +32729,13 @@
         <v>8</v>
       </c>
       <c r="D1231" t="s">
-        <v>264</v>
+        <v>125</v>
       </c>
       <c r="E1231" t="s">
-        <v>265</v>
+        <v>126</v>
       </c>
       <c r="F1231" t="s">
-        <v>2519</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1232" spans="1:6">
@@ -32737,13 +32749,13 @@
         <v>8</v>
       </c>
       <c r="D1232" t="s">
-        <v>201</v>
+        <v>264</v>
       </c>
       <c r="E1232" t="s">
-        <v>202</v>
+        <v>265</v>
       </c>
       <c r="F1232" t="s">
-        <v>2252</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="1233" spans="1:6">
@@ -32757,13 +32769,13 @@
         <v>8</v>
       </c>
       <c r="D1233" t="s">
-        <v>26</v>
+        <v>201</v>
       </c>
       <c r="E1233" t="s">
-        <v>27</v>
+        <v>202</v>
       </c>
       <c r="F1233" t="s">
-        <v>406</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1234" spans="1:6">
@@ -32777,13 +32789,13 @@
         <v>8</v>
       </c>
       <c r="D1234" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E1234" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F1234" t="s">
-        <v>63</v>
+        <v>406</v>
       </c>
     </row>
     <row r="1235" spans="1:6">
@@ -32797,13 +32809,13 @@
         <v>8</v>
       </c>
       <c r="D1235" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E1235" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F1235" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1236" spans="1:6">
@@ -32817,10 +32829,10 @@
         <v>8</v>
       </c>
       <c r="D1236" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E1236" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F1236" t="s">
         <v>28</v>
@@ -32837,13 +32849,13 @@
         <v>8</v>
       </c>
       <c r="D1237" t="s">
-        <v>125</v>
+        <v>31</v>
       </c>
       <c r="E1237" t="s">
-        <v>126</v>
+        <v>32</v>
       </c>
       <c r="F1237" t="s">
-        <v>1366</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1238" spans="1:6">
@@ -32857,13 +32869,13 @@
         <v>8</v>
       </c>
       <c r="D1238" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="E1238" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="F1238" t="s">
-        <v>429</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="1239" spans="1:6">
@@ -32877,32 +32889,72 @@
         <v>8</v>
       </c>
       <c r="D1239" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="E1239" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="F1239" t="s">
-        <v>2583</v>
+        <v>429</v>
       </c>
     </row>
     <row r="1240" spans="1:6">
       <c r="A1240" t="s">
+        <v>2583</v>
+      </c>
+      <c r="B1240" t="s">
         <v>2584</v>
       </c>
-      <c r="B1240" t="s">
+      <c r="C1240" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1240" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1240" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1240" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:6">
+      <c r="A1241" t="s">
         <v>2585</v>
       </c>
-      <c r="C1240" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1240" t="s">
+      <c r="B1241" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C1241" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1241" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1241" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1241" t="s">
+        <v>2587</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:6">
+      <c r="A1242" t="s">
+        <v>2588</v>
+      </c>
+      <c r="B1242" t="s">
+        <v>2589</v>
+      </c>
+      <c r="C1242" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1242" t="s">
         <v>31</v>
       </c>
-      <c r="E1240" t="s">
+      <c r="E1242" t="s">
         <v>32</v>
       </c>
-      <c r="F1240" t="s">
+      <c r="F1242" t="s">
         <v>21</v>
       </c>
     </row>

--- a/api/clv3/xlsx/en/ReportingOrganisation.xlsx
+++ b/api/clv3/xlsx/en/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7458" uniqueCount="2592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7470" uniqueCount="2596">
   <si>
     <t>code</t>
   </si>
@@ -25,15 +25,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:organisation-type-code</t>
+  </si>
+  <si>
+    <t>codeforiati:hq-country-or-region</t>
+  </si>
+  <si>
     <t>codeforiati:organisation-type</t>
   </si>
   <si>
-    <t>codeforiati:hq-country-or-region</t>
-  </si>
-  <si>
-    <t>codeforiati:organisation-type-code</t>
-  </si>
-  <si>
     <t>AU-5</t>
   </si>
   <si>
@@ -43,45 +43,45 @@
     <t>active</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
     <t>Government</t>
   </si>
   <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>44000</t>
   </si>
   <si>
     <t>The World Bank</t>
   </si>
   <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>(No country assigned)</t>
+  </si>
+  <si>
     <t>Multilateral</t>
   </si>
   <si>
-    <t>(No country assigned)</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>US-EIN-941655673</t>
   </si>
   <si>
     <t>The William and Flora Hewlett Foundation</t>
   </si>
   <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
     <t>Foundation</t>
   </si>
   <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>41AAA</t>
   </si>
   <si>
@@ -94,27 +94,27 @@
     <t>Frontline AIDS</t>
   </si>
   <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
     <t>International NGO</t>
   </si>
   <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>XI-IATI-EC_DEVCO</t>
   </si>
   <si>
     <t>European Commission - Directorate-General for International Cooperation and Development</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>Other Public Sector</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>SE-0</t>
   </si>
   <si>
@@ -229,12 +229,12 @@
     <t>Gavi, the vaccine alliance</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>Public Private Partnership</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>US-EIN-300108263</t>
   </si>
   <si>
@@ -277,15 +277,15 @@
     <t>Young Innovations Pvt. Ltd</t>
   </si>
   <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>Nepal</t>
+  </si>
+  <si>
     <t>Academic, Training and Research</t>
   </si>
   <si>
-    <t>Nepal</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
     <t>GB-CHC-327421</t>
   </si>
   <si>
@@ -391,12 +391,12 @@
     <t>ICA:UK</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>National NGO</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>GB-CHC-298316</t>
   </si>
   <si>
@@ -619,15 +619,15 @@
     <t>Southern African Catholic Bishops' Conference Aids Office</t>
   </si>
   <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
     <t>Regional NGO</t>
   </si>
   <si>
-    <t>South Africa</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
     <t>30001</t>
   </si>
   <si>
@@ -808,12 +808,12 @@
     <t>Triple Line</t>
   </si>
   <si>
+    <t>70</t>
+  </si>
+  <si>
     <t>Private Sector</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>GB-CHC-1058991</t>
   </si>
   <si>
@@ -7165,6 +7165,12 @@
     <t>African Parks Network</t>
   </si>
   <si>
+    <t>GB-COH-06581421</t>
+  </si>
+  <si>
+    <t>The Institute for Strategic Dialogue</t>
+  </si>
+  <si>
     <t>ML-NIF-055000335T</t>
   </si>
   <si>
@@ -7199,6 +7205,12 @@
   </si>
   <si>
     <t>Nature and Development Foundation</t>
+  </si>
+  <si>
+    <t>BD-NAB-2004</t>
+  </si>
+  <si>
+    <t>Centre for Injury Prevention and Research, Bangladesh (CIPRB)</t>
   </si>
   <si>
     <t>XI-BRIDGE-1812689272</t>
@@ -8121,7 +8133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1243"/>
+  <dimension ref="A1:F1245"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -30935,13 +30947,13 @@
         <v>8</v>
       </c>
       <c r="D1141" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="E1141" t="s">
-        <v>1283</v>
+        <v>27</v>
       </c>
       <c r="F1141" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1142" spans="1:6">
@@ -30958,7 +30970,7 @@
         <v>26</v>
       </c>
       <c r="E1142" t="s">
-        <v>63</v>
+        <v>1283</v>
       </c>
       <c r="F1142" t="s">
         <v>28</v>
@@ -30978,7 +30990,7 @@
         <v>26</v>
       </c>
       <c r="E1143" t="s">
-        <v>328</v>
+        <v>63</v>
       </c>
       <c r="F1143" t="s">
         <v>28</v>
@@ -30998,7 +31010,7 @@
         <v>26</v>
       </c>
       <c r="E1144" t="s">
-        <v>429</v>
+        <v>328</v>
       </c>
       <c r="F1144" t="s">
         <v>28</v>
@@ -31018,7 +31030,7 @@
         <v>26</v>
       </c>
       <c r="E1145" t="s">
-        <v>35</v>
+        <v>429</v>
       </c>
       <c r="F1145" t="s">
         <v>28</v>
@@ -31035,13 +31047,13 @@
         <v>8</v>
       </c>
       <c r="D1146" t="s">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="E1146" t="s">
-        <v>477</v>
+        <v>35</v>
       </c>
       <c r="F1146" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1147" spans="1:6">
@@ -31055,13 +31067,13 @@
         <v>8</v>
       </c>
       <c r="D1147" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="E1147" t="s">
-        <v>20</v>
+        <v>477</v>
       </c>
       <c r="F1147" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1148" spans="1:6">
@@ -31075,13 +31087,13 @@
         <v>8</v>
       </c>
       <c r="D1148" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="E1148" t="s">
-        <v>20</v>
+        <v>797</v>
       </c>
       <c r="F1148" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1149" spans="1:6">
@@ -31095,13 +31107,13 @@
         <v>8</v>
       </c>
       <c r="D1149" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="E1149" t="s">
-        <v>1224</v>
+        <v>20</v>
       </c>
       <c r="F1149" t="s">
-        <v>126</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1150" spans="1:6">
@@ -31115,13 +31127,13 @@
         <v>8</v>
       </c>
       <c r="D1150" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="E1150" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F1150" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1151" spans="1:6">
@@ -31135,13 +31147,13 @@
         <v>8</v>
       </c>
       <c r="D1151" t="s">
-        <v>264</v>
+        <v>125</v>
       </c>
       <c r="E1151" t="s">
-        <v>63</v>
+        <v>1224</v>
       </c>
       <c r="F1151" t="s">
-        <v>265</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1152" spans="1:6">
@@ -31155,13 +31167,13 @@
         <v>8</v>
       </c>
       <c r="D1152" t="s">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="E1152" t="s">
-        <v>343</v>
+        <v>27</v>
       </c>
       <c r="F1152" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1153" spans="1:6">
@@ -31175,13 +31187,13 @@
         <v>8</v>
       </c>
       <c r="D1153" t="s">
-        <v>26</v>
+        <v>264</v>
       </c>
       <c r="E1153" t="s">
-        <v>429</v>
+        <v>63</v>
       </c>
       <c r="F1153" t="s">
-        <v>28</v>
+        <v>265</v>
       </c>
     </row>
     <row r="1154" spans="1:6">
@@ -31195,13 +31207,13 @@
         <v>8</v>
       </c>
       <c r="D1154" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="E1154" t="s">
-        <v>20</v>
+        <v>343</v>
       </c>
       <c r="F1154" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1155" spans="1:6">
@@ -31215,13 +31227,13 @@
         <v>8</v>
       </c>
       <c r="D1155" t="s">
-        <v>264</v>
+        <v>26</v>
       </c>
       <c r="E1155" t="s">
-        <v>27</v>
+        <v>429</v>
       </c>
       <c r="F1155" t="s">
-        <v>265</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1156" spans="1:6">
@@ -31235,13 +31247,13 @@
         <v>8</v>
       </c>
       <c r="D1156" t="s">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="E1156" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="F1156" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1157" spans="1:6">
@@ -31255,13 +31267,13 @@
         <v>8</v>
       </c>
       <c r="D1157" t="s">
-        <v>26</v>
+        <v>264</v>
       </c>
       <c r="E1157" t="s">
-        <v>406</v>
+        <v>27</v>
       </c>
       <c r="F1157" t="s">
-        <v>28</v>
+        <v>265</v>
       </c>
     </row>
     <row r="1158" spans="1:6">
@@ -31275,13 +31287,13 @@
         <v>8</v>
       </c>
       <c r="D1158" t="s">
-        <v>264</v>
+        <v>125</v>
       </c>
       <c r="E1158" t="s">
-        <v>909</v>
+        <v>88</v>
       </c>
       <c r="F1158" t="s">
-        <v>265</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1159" spans="1:6">
@@ -31295,13 +31307,13 @@
         <v>8</v>
       </c>
       <c r="D1159" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="E1159" t="s">
-        <v>373</v>
+        <v>406</v>
       </c>
       <c r="F1159" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1160" spans="1:6">
@@ -31315,13 +31327,13 @@
         <v>8</v>
       </c>
       <c r="D1160" t="s">
-        <v>125</v>
+        <v>264</v>
       </c>
       <c r="E1160" t="s">
-        <v>373</v>
+        <v>909</v>
       </c>
       <c r="F1160" t="s">
-        <v>126</v>
+        <v>265</v>
       </c>
     </row>
     <row r="1161" spans="1:6">
@@ -31335,13 +31347,13 @@
         <v>8</v>
       </c>
       <c r="D1161" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="E1161" t="s">
-        <v>27</v>
+        <v>373</v>
       </c>
       <c r="F1161" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1162" spans="1:6">
@@ -31355,13 +31367,13 @@
         <v>8</v>
       </c>
       <c r="D1162" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="E1162" t="s">
-        <v>63</v>
+        <v>373</v>
       </c>
       <c r="F1162" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1163" spans="1:6">
@@ -31375,13 +31387,13 @@
         <v>8</v>
       </c>
       <c r="D1163" t="s">
-        <v>125</v>
+        <v>14</v>
       </c>
       <c r="E1163" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="F1163" t="s">
-        <v>126</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1164" spans="1:6">
@@ -31395,13 +31407,13 @@
         <v>8</v>
       </c>
       <c r="D1164" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="E1164" t="s">
-        <v>1224</v>
+        <v>63</v>
       </c>
       <c r="F1164" t="s">
-        <v>126</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1165" spans="1:6">
@@ -31415,13 +31427,13 @@
         <v>8</v>
       </c>
       <c r="D1165" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="E1165" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="F1165" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1166" spans="1:6">
@@ -31435,13 +31447,13 @@
         <v>8</v>
       </c>
       <c r="D1166" t="s">
-        <v>14</v>
+        <v>125</v>
       </c>
       <c r="E1166" t="s">
-        <v>15</v>
+        <v>1224</v>
       </c>
       <c r="F1166" t="s">
-        <v>16</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1167" spans="1:6">
@@ -31455,13 +31467,13 @@
         <v>8</v>
       </c>
       <c r="D1167" t="s">
-        <v>201</v>
+        <v>26</v>
       </c>
       <c r="E1167" t="s">
-        <v>406</v>
+        <v>27</v>
       </c>
       <c r="F1167" t="s">
-        <v>203</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1168" spans="1:6">
@@ -31475,13 +31487,13 @@
         <v>8</v>
       </c>
       <c r="D1168" t="s">
-        <v>125</v>
+        <v>14</v>
       </c>
       <c r="E1168" t="s">
-        <v>1224</v>
+        <v>15</v>
       </c>
       <c r="F1168" t="s">
-        <v>126</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1169" spans="1:6">
@@ -31495,13 +31507,13 @@
         <v>8</v>
       </c>
       <c r="D1169" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E1169" t="s">
-        <v>1224</v>
+        <v>406</v>
       </c>
       <c r="F1169" t="s">
-        <v>11</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1170" spans="1:6">
@@ -31515,13 +31527,13 @@
         <v>8</v>
       </c>
       <c r="D1170" t="s">
-        <v>264</v>
+        <v>125</v>
       </c>
       <c r="E1170" t="s">
-        <v>1366</v>
+        <v>1224</v>
       </c>
       <c r="F1170" t="s">
-        <v>265</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1171" spans="1:6">
@@ -31535,13 +31547,13 @@
         <v>8</v>
       </c>
       <c r="D1171" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
       <c r="E1171" t="s">
-        <v>2363</v>
+        <v>1224</v>
       </c>
       <c r="F1171" t="s">
-        <v>265</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1172" spans="1:6">
@@ -31555,13 +31567,13 @@
         <v>8</v>
       </c>
       <c r="D1172" t="s">
-        <v>125</v>
+        <v>264</v>
       </c>
       <c r="E1172" t="s">
-        <v>38</v>
+        <v>1366</v>
       </c>
       <c r="F1172" t="s">
-        <v>126</v>
+        <v>265</v>
       </c>
     </row>
     <row r="1173" spans="1:6">
@@ -31575,13 +31587,13 @@
         <v>8</v>
       </c>
       <c r="D1173" t="s">
-        <v>125</v>
+        <v>264</v>
       </c>
       <c r="E1173" t="s">
-        <v>1809</v>
+        <v>2363</v>
       </c>
       <c r="F1173" t="s">
-        <v>126</v>
+        <v>265</v>
       </c>
     </row>
     <row r="1174" spans="1:6">
@@ -31595,13 +31607,13 @@
         <v>8</v>
       </c>
       <c r="D1174" t="s">
-        <v>71</v>
+        <v>125</v>
       </c>
       <c r="E1174" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="F1174" t="s">
-        <v>72</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1175" spans="1:6">
@@ -31615,13 +31627,13 @@
         <v>8</v>
       </c>
       <c r="D1175" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="E1175" t="s">
-        <v>20</v>
+        <v>1809</v>
       </c>
       <c r="F1175" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1176" spans="1:6">
@@ -31635,13 +31647,13 @@
         <v>8</v>
       </c>
       <c r="D1176" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="E1176" t="s">
-        <v>373</v>
+        <v>53</v>
       </c>
       <c r="F1176" t="s">
-        <v>126</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1177" spans="1:6">
@@ -31655,13 +31667,13 @@
         <v>8</v>
       </c>
       <c r="D1177" t="s">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="E1177" t="s">
-        <v>1634</v>
+        <v>20</v>
       </c>
       <c r="F1177" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1178" spans="1:6">
@@ -31675,13 +31687,13 @@
         <v>8</v>
       </c>
       <c r="D1178" t="s">
-        <v>264</v>
+        <v>125</v>
       </c>
       <c r="E1178" t="s">
-        <v>63</v>
+        <v>373</v>
       </c>
       <c r="F1178" t="s">
-        <v>265</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1179" spans="1:6">
@@ -31695,13 +31707,13 @@
         <v>8</v>
       </c>
       <c r="D1179" t="s">
-        <v>19</v>
+        <v>125</v>
       </c>
       <c r="E1179" t="s">
-        <v>63</v>
+        <v>1634</v>
       </c>
       <c r="F1179" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1180" spans="1:6">
@@ -31715,13 +31727,13 @@
         <v>8</v>
       </c>
       <c r="D1180" t="s">
-        <v>125</v>
+        <v>264</v>
       </c>
       <c r="E1180" t="s">
-        <v>1809</v>
+        <v>63</v>
       </c>
       <c r="F1180" t="s">
-        <v>126</v>
+        <v>265</v>
       </c>
     </row>
     <row r="1181" spans="1:6">
@@ -31735,13 +31747,13 @@
         <v>8</v>
       </c>
       <c r="D1181" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E1181" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="F1181" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1182" spans="1:6">
@@ -31755,13 +31767,13 @@
         <v>8</v>
       </c>
       <c r="D1182" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="E1182" t="s">
-        <v>63</v>
+        <v>1809</v>
       </c>
       <c r="F1182" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1183" spans="1:6">
@@ -31778,7 +31790,7 @@
         <v>26</v>
       </c>
       <c r="E1183" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="F1183" t="s">
         <v>28</v>
@@ -31798,7 +31810,7 @@
         <v>26</v>
       </c>
       <c r="E1184" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="F1184" t="s">
         <v>28</v>
@@ -31815,13 +31827,13 @@
         <v>8</v>
       </c>
       <c r="D1185" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="E1185" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="F1185" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1186" spans="1:6">
@@ -31838,7 +31850,7 @@
         <v>26</v>
       </c>
       <c r="E1186" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F1186" t="s">
         <v>28</v>
@@ -31855,13 +31867,13 @@
         <v>8</v>
       </c>
       <c r="D1187" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="E1187" t="s">
         <v>63</v>
       </c>
       <c r="F1187" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1188" spans="1:6">
@@ -31878,7 +31890,7 @@
         <v>26</v>
       </c>
       <c r="E1188" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F1188" t="s">
         <v>28</v>
@@ -31895,13 +31907,13 @@
         <v>8</v>
       </c>
       <c r="D1189" t="s">
-        <v>264</v>
+        <v>19</v>
       </c>
       <c r="E1189" t="s">
         <v>63</v>
       </c>
       <c r="F1189" t="s">
-        <v>265</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1190" spans="1:6">
@@ -31918,7 +31930,7 @@
         <v>26</v>
       </c>
       <c r="E1190" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="F1190" t="s">
         <v>28</v>
@@ -31935,13 +31947,13 @@
         <v>8</v>
       </c>
       <c r="D1191" t="s">
-        <v>19</v>
+        <v>264</v>
       </c>
       <c r="E1191" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="F1191" t="s">
-        <v>21</v>
+        <v>265</v>
       </c>
     </row>
     <row r="1192" spans="1:6">
@@ -31955,13 +31967,13 @@
         <v>8</v>
       </c>
       <c r="D1192" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E1192" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="F1192" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1193" spans="1:6">
@@ -31975,13 +31987,13 @@
         <v>8</v>
       </c>
       <c r="D1193" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E1193" t="s">
         <v>27</v>
       </c>
       <c r="F1193" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1194" spans="1:6">
@@ -31995,13 +32007,13 @@
         <v>8</v>
       </c>
       <c r="D1194" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="E1194" t="s">
         <v>27</v>
       </c>
       <c r="F1194" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1195" spans="1:6">
@@ -32015,13 +32027,13 @@
         <v>8</v>
       </c>
       <c r="D1195" t="s">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="E1195" t="s">
         <v>27</v>
       </c>
       <c r="F1195" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1196" spans="1:6">
@@ -32055,13 +32067,13 @@
         <v>8</v>
       </c>
       <c r="D1197" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="E1197" t="s">
         <v>27</v>
       </c>
       <c r="F1197" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1198" spans="1:6">
@@ -32075,13 +32087,13 @@
         <v>8</v>
       </c>
       <c r="D1198" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="E1198" t="s">
         <v>27</v>
       </c>
       <c r="F1198" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1199" spans="1:6">
@@ -32095,13 +32107,13 @@
         <v>8</v>
       </c>
       <c r="D1199" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E1199" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F1199" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1200" spans="1:6">
@@ -32115,13 +32127,13 @@
         <v>8</v>
       </c>
       <c r="D1200" t="s">
-        <v>264</v>
+        <v>26</v>
       </c>
       <c r="E1200" t="s">
         <v>27</v>
       </c>
       <c r="F1200" t="s">
-        <v>265</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1201" spans="1:6">
@@ -32135,13 +32147,13 @@
         <v>8</v>
       </c>
       <c r="D1201" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E1201" t="s">
         <v>20</v>
       </c>
       <c r="F1201" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1202" spans="1:6">
@@ -32155,13 +32167,13 @@
         <v>8</v>
       </c>
       <c r="D1202" t="s">
-        <v>87</v>
+        <v>264</v>
       </c>
       <c r="E1202" t="s">
         <v>27</v>
       </c>
       <c r="F1202" t="s">
-        <v>89</v>
+        <v>265</v>
       </c>
     </row>
     <row r="1203" spans="1:6">
@@ -32175,13 +32187,13 @@
         <v>8</v>
       </c>
       <c r="D1203" t="s">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="E1203" t="s">
-        <v>1283</v>
+        <v>20</v>
       </c>
       <c r="F1203" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1204" spans="1:6">
@@ -32215,13 +32227,13 @@
         <v>8</v>
       </c>
       <c r="D1205" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="E1205" t="s">
-        <v>38</v>
+        <v>1283</v>
       </c>
       <c r="F1205" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1206" spans="1:6">
@@ -32235,13 +32247,13 @@
         <v>8</v>
       </c>
       <c r="D1206" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="E1206" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="F1206" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1207" spans="1:6">
@@ -32255,13 +32267,13 @@
         <v>8</v>
       </c>
       <c r="D1207" t="s">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="E1207" t="s">
-        <v>1809</v>
+        <v>38</v>
       </c>
       <c r="F1207" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1208" spans="1:6">
@@ -32275,21 +32287,21 @@
         <v>8</v>
       </c>
       <c r="D1208" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="E1208" t="s">
-        <v>2519</v>
+        <v>63</v>
       </c>
       <c r="F1208" t="s">
-        <v>126</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1209" spans="1:6">
       <c r="A1209" t="s">
+        <v>2519</v>
+      </c>
+      <c r="B1209" t="s">
         <v>2520</v>
-      </c>
-      <c r="B1209" t="s">
-        <v>2521</v>
       </c>
       <c r="C1209" t="s">
         <v>8</v>
@@ -32298,7 +32310,7 @@
         <v>125</v>
       </c>
       <c r="E1209" t="s">
-        <v>1366</v>
+        <v>1809</v>
       </c>
       <c r="F1209" t="s">
         <v>126</v>
@@ -32306,10 +32318,10 @@
     </row>
     <row r="1210" spans="1:6">
       <c r="A1210" t="s">
+        <v>2521</v>
+      </c>
+      <c r="B1210" t="s">
         <v>2522</v>
-      </c>
-      <c r="B1210" t="s">
-        <v>2523</v>
       </c>
       <c r="C1210" t="s">
         <v>8</v>
@@ -32318,7 +32330,7 @@
         <v>125</v>
       </c>
       <c r="E1210" t="s">
-        <v>2252</v>
+        <v>2523</v>
       </c>
       <c r="F1210" t="s">
         <v>126</v>
@@ -32335,13 +32347,13 @@
         <v>8</v>
       </c>
       <c r="D1211" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="E1211" t="s">
-        <v>20</v>
+        <v>1366</v>
       </c>
       <c r="F1211" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1212" spans="1:6">
@@ -32355,22 +32367,22 @@
         <v>8</v>
       </c>
       <c r="D1212" t="s">
-        <v>19</v>
+        <v>125</v>
       </c>
       <c r="E1212" t="s">
-        <v>2528</v>
+        <v>2252</v>
       </c>
       <c r="F1212" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1213" spans="1:6">
       <c r="A1213" t="s">
+        <v>2528</v>
+      </c>
+      <c r="B1213" t="s">
         <v>2529</v>
       </c>
-      <c r="B1213" t="s">
-        <v>2530</v>
-      </c>
       <c r="C1213" t="s">
         <v>8</v>
       </c>
@@ -32378,7 +32390,7 @@
         <v>26</v>
       </c>
       <c r="E1213" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F1213" t="s">
         <v>28</v>
@@ -32386,22 +32398,22 @@
     </row>
     <row r="1214" spans="1:6">
       <c r="A1214" t="s">
+        <v>2530</v>
+      </c>
+      <c r="B1214" t="s">
         <v>2531</v>
       </c>
-      <c r="B1214" t="s">
+      <c r="C1214" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1214" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1214" t="s">
         <v>2532</v>
       </c>
-      <c r="C1214" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1214" t="s">
-        <v>87</v>
-      </c>
-      <c r="E1214" t="s">
-        <v>27</v>
-      </c>
       <c r="F1214" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1215" spans="1:6">
@@ -32415,13 +32427,13 @@
         <v>8</v>
       </c>
       <c r="D1215" t="s">
-        <v>264</v>
+        <v>26</v>
       </c>
       <c r="E1215" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="F1215" t="s">
-        <v>265</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1216" spans="1:6">
@@ -32435,13 +32447,13 @@
         <v>8</v>
       </c>
       <c r="D1216" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="E1216" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F1216" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1217" spans="1:6">
@@ -32455,13 +32467,13 @@
         <v>8</v>
       </c>
       <c r="D1217" t="s">
-        <v>9</v>
+        <v>264</v>
       </c>
       <c r="E1217" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="F1217" t="s">
-        <v>11</v>
+        <v>265</v>
       </c>
     </row>
     <row r="1218" spans="1:6">
@@ -32478,7 +32490,7 @@
         <v>26</v>
       </c>
       <c r="E1218" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F1218" t="s">
         <v>28</v>
@@ -32495,13 +32507,13 @@
         <v>8</v>
       </c>
       <c r="D1219" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E1219" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F1219" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1220" spans="1:6">
@@ -32515,13 +32527,13 @@
         <v>8</v>
       </c>
       <c r="D1220" t="s">
-        <v>264</v>
+        <v>26</v>
       </c>
       <c r="E1220" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="F1220" t="s">
-        <v>265</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1221" spans="1:6">
@@ -32535,13 +32547,13 @@
         <v>8</v>
       </c>
       <c r="D1221" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="E1221" t="s">
-        <v>202</v>
+        <v>20</v>
       </c>
       <c r="F1221" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1222" spans="1:6">
@@ -32555,13 +32567,13 @@
         <v>8</v>
       </c>
       <c r="D1222" t="s">
-        <v>19</v>
+        <v>264</v>
       </c>
       <c r="E1222" t="s">
-        <v>1366</v>
+        <v>27</v>
       </c>
       <c r="F1222" t="s">
-        <v>21</v>
+        <v>265</v>
       </c>
     </row>
     <row r="1223" spans="1:6">
@@ -32575,13 +32587,13 @@
         <v>8</v>
       </c>
       <c r="D1223" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="E1223" t="s">
-        <v>27</v>
+        <v>202</v>
       </c>
       <c r="F1223" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1224" spans="1:6">
@@ -32595,13 +32607,13 @@
         <v>8</v>
       </c>
       <c r="D1224" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E1224" t="s">
-        <v>38</v>
+        <v>1366</v>
       </c>
       <c r="F1224" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1225" spans="1:6">
@@ -32635,13 +32647,13 @@
         <v>8</v>
       </c>
       <c r="D1226" t="s">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="E1226" t="s">
-        <v>2252</v>
+        <v>38</v>
       </c>
       <c r="F1226" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1227" spans="1:6">
@@ -32655,13 +32667,13 @@
         <v>8</v>
       </c>
       <c r="D1227" t="s">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="E1227" t="s">
-        <v>2519</v>
+        <v>27</v>
       </c>
       <c r="F1227" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1228" spans="1:6">
@@ -32675,13 +32687,13 @@
         <v>8</v>
       </c>
       <c r="D1228" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="E1228" t="s">
-        <v>27</v>
+        <v>2252</v>
       </c>
       <c r="F1228" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1229" spans="1:6">
@@ -32695,13 +32707,13 @@
         <v>8</v>
       </c>
       <c r="D1229" t="s">
-        <v>264</v>
+        <v>125</v>
       </c>
       <c r="E1229" t="s">
-        <v>1366</v>
+        <v>2523</v>
       </c>
       <c r="F1229" t="s">
-        <v>265</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1230" spans="1:6">
@@ -32715,13 +32727,13 @@
         <v>8</v>
       </c>
       <c r="D1230" t="s">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="E1230" t="s">
-        <v>797</v>
+        <v>27</v>
       </c>
       <c r="F1230" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1231" spans="1:6">
@@ -32735,13 +32747,13 @@
         <v>8</v>
       </c>
       <c r="D1231" t="s">
-        <v>125</v>
+        <v>264</v>
       </c>
       <c r="E1231" t="s">
-        <v>20</v>
+        <v>1366</v>
       </c>
       <c r="F1231" t="s">
-        <v>126</v>
+        <v>265</v>
       </c>
     </row>
     <row r="1232" spans="1:6">
@@ -32755,13 +32767,13 @@
         <v>8</v>
       </c>
       <c r="D1232" t="s">
-        <v>264</v>
+        <v>125</v>
       </c>
       <c r="E1232" t="s">
-        <v>2519</v>
+        <v>797</v>
       </c>
       <c r="F1232" t="s">
-        <v>265</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1233" spans="1:6">
@@ -32775,13 +32787,13 @@
         <v>8</v>
       </c>
       <c r="D1233" t="s">
-        <v>201</v>
+        <v>125</v>
       </c>
       <c r="E1233" t="s">
-        <v>2252</v>
+        <v>20</v>
       </c>
       <c r="F1233" t="s">
-        <v>203</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1234" spans="1:6">
@@ -32795,13 +32807,13 @@
         <v>8</v>
       </c>
       <c r="D1234" t="s">
-        <v>26</v>
+        <v>264</v>
       </c>
       <c r="E1234" t="s">
-        <v>406</v>
+        <v>2523</v>
       </c>
       <c r="F1234" t="s">
-        <v>28</v>
+        <v>265</v>
       </c>
     </row>
     <row r="1235" spans="1:6">
@@ -32815,13 +32827,13 @@
         <v>8</v>
       </c>
       <c r="D1235" t="s">
-        <v>31</v>
+        <v>201</v>
       </c>
       <c r="E1235" t="s">
-        <v>63</v>
+        <v>2252</v>
       </c>
       <c r="F1235" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1236" spans="1:6">
@@ -32838,7 +32850,7 @@
         <v>26</v>
       </c>
       <c r="E1236" t="s">
-        <v>27</v>
+        <v>406</v>
       </c>
       <c r="F1236" t="s">
         <v>28</v>
@@ -32858,7 +32870,7 @@
         <v>31</v>
       </c>
       <c r="E1237" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="F1237" t="s">
         <v>32</v>
@@ -32875,13 +32887,13 @@
         <v>8</v>
       </c>
       <c r="D1238" t="s">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="E1238" t="s">
-        <v>1366</v>
+        <v>27</v>
       </c>
       <c r="F1238" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1239" spans="1:6">
@@ -32895,13 +32907,13 @@
         <v>8</v>
       </c>
       <c r="D1239" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="E1239" t="s">
-        <v>429</v>
+        <v>27</v>
       </c>
       <c r="F1239" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1240" spans="1:6">
@@ -32918,7 +32930,7 @@
         <v>125</v>
       </c>
       <c r="E1240" t="s">
-        <v>373</v>
+        <v>1366</v>
       </c>
       <c r="F1240" t="s">
         <v>126</v>
@@ -32935,52 +32947,92 @@
         <v>8</v>
       </c>
       <c r="D1241" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="E1241" t="s">
-        <v>2587</v>
+        <v>429</v>
       </c>
       <c r="F1241" t="s">
-        <v>126</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1242" spans="1:6">
       <c r="A1242" t="s">
+        <v>2587</v>
+      </c>
+      <c r="B1242" t="s">
         <v>2588</v>
       </c>
-      <c r="B1242" t="s">
-        <v>2589</v>
-      </c>
       <c r="C1242" t="s">
         <v>8</v>
       </c>
       <c r="D1242" t="s">
-        <v>31</v>
+        <v>125</v>
       </c>
       <c r="E1242" t="s">
-        <v>20</v>
+        <v>373</v>
       </c>
       <c r="F1242" t="s">
-        <v>32</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1243" spans="1:6">
       <c r="A1243" t="s">
+        <v>2589</v>
+      </c>
+      <c r="B1243" t="s">
         <v>2590</v>
       </c>
-      <c r="B1243" t="s">
+      <c r="C1243" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1243" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1243" t="s">
         <v>2591</v>
       </c>
-      <c r="C1243" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1243" t="s">
+      <c r="F1243" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:6">
+      <c r="A1244" t="s">
+        <v>2592</v>
+      </c>
+      <c r="B1244" t="s">
+        <v>2593</v>
+      </c>
+      <c r="C1244" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1244" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1244" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1244" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:6">
+      <c r="A1245" t="s">
+        <v>2594</v>
+      </c>
+      <c r="B1245" t="s">
+        <v>2595</v>
+      </c>
+      <c r="C1245" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1245" t="s">
         <v>87</v>
       </c>
-      <c r="E1243" t="s">
+      <c r="E1245" t="s">
         <v>20</v>
       </c>
-      <c r="F1243" t="s">
+      <c r="F1245" t="s">
         <v>89</v>
       </c>
     </row>

--- a/api/clv3/xlsx/en/ReportingOrganisation.xlsx
+++ b/api/clv3/xlsx/en/ReportingOrganisation.xlsx
@@ -25,15 +25,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:organisation-type</t>
+  </si>
+  <si>
+    <t>codeforiati:hq-country-or-region</t>
+  </si>
+  <si>
     <t>codeforiati:organisation-type-code</t>
   </si>
   <si>
-    <t>codeforiati:hq-country-or-region</t>
-  </si>
-  <si>
-    <t>codeforiati:organisation-type</t>
-  </si>
-  <si>
     <t>AU-5</t>
   </si>
   <si>
@@ -43,45 +43,45 @@
     <t>active</t>
   </si>
   <si>
+    <t>Government</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>Government</t>
-  </si>
-  <si>
     <t>44000</t>
   </si>
   <si>
     <t>The World Bank</t>
   </si>
   <si>
+    <t>Multilateral</t>
+  </si>
+  <si>
+    <t>(No country assigned)</t>
+  </si>
+  <si>
     <t>40</t>
   </si>
   <si>
-    <t>(No country assigned)</t>
-  </si>
-  <si>
-    <t>Multilateral</t>
-  </si>
-  <si>
     <t>US-EIN-941655673</t>
   </si>
   <si>
     <t>The William and Flora Hewlett Foundation</t>
   </si>
   <si>
+    <t>Foundation</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
     <t>60</t>
   </si>
   <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>Foundation</t>
-  </si>
-  <si>
     <t>41AAA</t>
   </si>
   <si>
@@ -94,27 +94,27 @@
     <t>Frontline AIDS</t>
   </si>
   <si>
+    <t>International NGO</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
     <t>21</t>
   </si>
   <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>International NGO</t>
-  </si>
-  <si>
     <t>XI-IATI-EC_DEVCO</t>
   </si>
   <si>
     <t>European Commission - Directorate-General for International Cooperation and Development</t>
   </si>
   <si>
+    <t>Other Public Sector</t>
+  </si>
+  <si>
     <t>15</t>
   </si>
   <si>
-    <t>Other Public Sector</t>
-  </si>
-  <si>
     <t>SE-0</t>
   </si>
   <si>
@@ -229,12 +229,12 @@
     <t>Gavi, the vaccine alliance</t>
   </si>
   <si>
+    <t>Public Private Partnership</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
-    <t>Public Private Partnership</t>
-  </si>
-  <si>
     <t>US-EIN-300108263</t>
   </si>
   <si>
@@ -277,15 +277,15 @@
     <t>Young Innovations Pvt. Ltd</t>
   </si>
   <si>
+    <t>Academic, Training and Research</t>
+  </si>
+  <si>
+    <t>Nepal</t>
+  </si>
+  <si>
     <t>80</t>
   </si>
   <si>
-    <t>Nepal</t>
-  </si>
-  <si>
-    <t>Academic, Training and Research</t>
-  </si>
-  <si>
     <t>GB-CHC-327421</t>
   </si>
   <si>
@@ -391,12 +391,12 @@
     <t>ICA:UK</t>
   </si>
   <si>
+    <t>National NGO</t>
+  </si>
+  <si>
     <t>22</t>
   </si>
   <si>
-    <t>National NGO</t>
-  </si>
-  <si>
     <t>GB-CHC-298316</t>
   </si>
   <si>
@@ -619,15 +619,15 @@
     <t>Southern African Catholic Bishops' Conference Aids Office</t>
   </si>
   <si>
+    <t>Regional NGO</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
     <t>23</t>
   </si>
   <si>
-    <t>South Africa</t>
-  </si>
-  <si>
-    <t>Regional NGO</t>
-  </si>
-  <si>
     <t>30001</t>
   </si>
   <si>
@@ -808,10 +808,10 @@
     <t>Triple Line</t>
   </si>
   <si>
+    <t>Private Sector</t>
+  </si>
+  <si>
     <t>70</t>
-  </si>
-  <si>
-    <t>Private Sector</t>
   </si>
   <si>
     <t>GB-CHC-1058991</t>

--- a/api/clv3/xlsx/en/ReportingOrganisation.xlsx
+++ b/api/clv3/xlsx/en/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7566" uniqueCount="2630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7572" uniqueCount="2632">
   <si>
     <t>code</t>
   </si>
@@ -7649,6 +7649,12 @@
   </si>
   <si>
     <t>NLR Indonesia</t>
+  </si>
+  <si>
+    <t>GB-CHC-1076722</t>
+  </si>
+  <si>
+    <t>TRAFFIC International</t>
   </si>
   <si>
     <t>US-EIN-81-2339233</t>
@@ -8235,7 +8241,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1261"/>
+  <dimension ref="A1:F1262"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -32669,13 +32675,13 @@
         <v>8</v>
       </c>
       <c r="D1222" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="E1222" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F1222" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1223" spans="1:6">
@@ -32689,33 +32695,33 @@
         <v>8</v>
       </c>
       <c r="D1223" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E1223" t="s">
-        <v>2549</v>
+        <v>20</v>
       </c>
       <c r="F1223" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1224" spans="1:6">
       <c r="A1224" t="s">
+        <v>2549</v>
+      </c>
+      <c r="B1224" t="s">
         <v>2550</v>
       </c>
-      <c r="B1224" t="s">
+      <c r="C1224" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1224" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1224" t="s">
         <v>2551</v>
       </c>
-      <c r="C1224" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1224" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1224" t="s">
-        <v>27</v>
-      </c>
       <c r="F1224" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1225" spans="1:6">
@@ -32729,13 +32735,13 @@
         <v>8</v>
       </c>
       <c r="D1225" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="E1225" t="s">
         <v>27</v>
       </c>
       <c r="F1225" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1226" spans="1:6">
@@ -32749,13 +32755,13 @@
         <v>8</v>
       </c>
       <c r="D1226" t="s">
-        <v>266</v>
+        <v>87</v>
       </c>
       <c r="E1226" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="F1226" t="s">
-        <v>267</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1227" spans="1:6">
@@ -32769,13 +32775,13 @@
         <v>8</v>
       </c>
       <c r="D1227" t="s">
-        <v>26</v>
+        <v>266</v>
       </c>
       <c r="E1227" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="F1227" t="s">
-        <v>28</v>
+        <v>267</v>
       </c>
     </row>
     <row r="1228" spans="1:6">
@@ -32789,13 +32795,13 @@
         <v>8</v>
       </c>
       <c r="D1228" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E1228" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="F1228" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1229" spans="1:6">
@@ -32809,13 +32815,13 @@
         <v>8</v>
       </c>
       <c r="D1229" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E1229" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="F1229" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1230" spans="1:6">
@@ -32832,7 +32838,7 @@
         <v>26</v>
       </c>
       <c r="E1230" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="F1230" t="s">
         <v>28</v>
@@ -32849,13 +32855,13 @@
         <v>8</v>
       </c>
       <c r="D1231" t="s">
-        <v>266</v>
+        <v>26</v>
       </c>
       <c r="E1231" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F1231" t="s">
-        <v>267</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1232" spans="1:6">
@@ -32869,13 +32875,13 @@
         <v>8</v>
       </c>
       <c r="D1232" t="s">
-        <v>87</v>
+        <v>266</v>
       </c>
       <c r="E1232" t="s">
-        <v>202</v>
+        <v>27</v>
       </c>
       <c r="F1232" t="s">
-        <v>89</v>
+        <v>267</v>
       </c>
     </row>
     <row r="1233" spans="1:6">
@@ -32889,13 +32895,13 @@
         <v>8</v>
       </c>
       <c r="D1233" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="E1233" t="s">
-        <v>496</v>
+        <v>202</v>
       </c>
       <c r="F1233" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1234" spans="1:6">
@@ -32909,13 +32915,13 @@
         <v>8</v>
       </c>
       <c r="D1234" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="E1234" t="s">
-        <v>27</v>
+        <v>496</v>
       </c>
       <c r="F1234" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1235" spans="1:6">
@@ -32929,13 +32935,13 @@
         <v>8</v>
       </c>
       <c r="D1235" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="E1235" t="s">
         <v>27</v>
       </c>
       <c r="F1235" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1236" spans="1:6">
@@ -32952,7 +32958,7 @@
         <v>26</v>
       </c>
       <c r="E1236" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F1236" t="s">
         <v>28</v>
@@ -32972,7 +32978,7 @@
         <v>26</v>
       </c>
       <c r="E1237" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F1237" t="s">
         <v>28</v>
@@ -32989,13 +32995,13 @@
         <v>8</v>
       </c>
       <c r="D1238" t="s">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="E1238" t="s">
-        <v>2264</v>
+        <v>27</v>
       </c>
       <c r="F1238" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1239" spans="1:6">
@@ -33012,7 +33018,7 @@
         <v>125</v>
       </c>
       <c r="E1239" t="s">
-        <v>2538</v>
+        <v>2264</v>
       </c>
       <c r="F1239" t="s">
         <v>126</v>
@@ -33029,13 +33035,13 @@
         <v>8</v>
       </c>
       <c r="D1240" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="E1240" t="s">
-        <v>27</v>
+        <v>2538</v>
       </c>
       <c r="F1240" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1241" spans="1:6">
@@ -33049,13 +33055,13 @@
         <v>8</v>
       </c>
       <c r="D1241" t="s">
-        <v>266</v>
+        <v>26</v>
       </c>
       <c r="E1241" t="s">
-        <v>496</v>
+        <v>27</v>
       </c>
       <c r="F1241" t="s">
-        <v>267</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1242" spans="1:6">
@@ -33069,13 +33075,13 @@
         <v>8</v>
       </c>
       <c r="D1242" t="s">
-        <v>125</v>
+        <v>266</v>
       </c>
       <c r="E1242" t="s">
-        <v>804</v>
+        <v>496</v>
       </c>
       <c r="F1242" t="s">
-        <v>126</v>
+        <v>267</v>
       </c>
     </row>
     <row r="1243" spans="1:6">
@@ -33092,7 +33098,7 @@
         <v>125</v>
       </c>
       <c r="E1243" t="s">
-        <v>20</v>
+        <v>804</v>
       </c>
       <c r="F1243" t="s">
         <v>126</v>
@@ -33109,13 +33115,13 @@
         <v>8</v>
       </c>
       <c r="D1244" t="s">
-        <v>266</v>
+        <v>125</v>
       </c>
       <c r="E1244" t="s">
-        <v>2538</v>
+        <v>20</v>
       </c>
       <c r="F1244" t="s">
-        <v>267</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1245" spans="1:6">
@@ -33129,13 +33135,13 @@
         <v>8</v>
       </c>
       <c r="D1245" t="s">
-        <v>201</v>
+        <v>266</v>
       </c>
       <c r="E1245" t="s">
-        <v>2264</v>
+        <v>2538</v>
       </c>
       <c r="F1245" t="s">
-        <v>203</v>
+        <v>267</v>
       </c>
     </row>
     <row r="1246" spans="1:6">
@@ -33149,13 +33155,13 @@
         <v>8</v>
       </c>
       <c r="D1246" t="s">
-        <v>26</v>
+        <v>201</v>
       </c>
       <c r="E1246" t="s">
-        <v>408</v>
+        <v>2264</v>
       </c>
       <c r="F1246" t="s">
-        <v>28</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1247" spans="1:6">
@@ -33169,13 +33175,13 @@
         <v>8</v>
       </c>
       <c r="D1247" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E1247" t="s">
-        <v>63</v>
+        <v>408</v>
       </c>
       <c r="F1247" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1248" spans="1:6">
@@ -33189,13 +33195,13 @@
         <v>8</v>
       </c>
       <c r="D1248" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E1248" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="F1248" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1249" spans="1:6">
@@ -33209,13 +33215,13 @@
         <v>8</v>
       </c>
       <c r="D1249" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E1249" t="s">
         <v>27</v>
       </c>
       <c r="F1249" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1250" spans="1:6">
@@ -33229,13 +33235,13 @@
         <v>8</v>
       </c>
       <c r="D1250" t="s">
-        <v>125</v>
+        <v>31</v>
       </c>
       <c r="E1250" t="s">
-        <v>496</v>
+        <v>27</v>
       </c>
       <c r="F1250" t="s">
-        <v>126</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1251" spans="1:6">
@@ -33249,13 +33255,13 @@
         <v>8</v>
       </c>
       <c r="D1251" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="E1251" t="s">
-        <v>27</v>
+        <v>496</v>
       </c>
       <c r="F1251" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1252" spans="1:6">
@@ -33272,7 +33278,7 @@
         <v>87</v>
       </c>
       <c r="E1252" t="s">
-        <v>431</v>
+        <v>27</v>
       </c>
       <c r="F1252" t="s">
         <v>89</v>
@@ -33289,13 +33295,13 @@
         <v>8</v>
       </c>
       <c r="D1253" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="E1253" t="s">
-        <v>375</v>
+        <v>431</v>
       </c>
       <c r="F1253" t="s">
-        <v>126</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1254" spans="1:6">
@@ -33312,7 +33318,7 @@
         <v>125</v>
       </c>
       <c r="E1254" t="s">
-        <v>2612</v>
+        <v>375</v>
       </c>
       <c r="F1254" t="s">
         <v>126</v>
@@ -33320,22 +33326,22 @@
     </row>
     <row r="1255" spans="1:6">
       <c r="A1255" t="s">
+        <v>2612</v>
+      </c>
+      <c r="B1255" t="s">
         <v>2613</v>
       </c>
-      <c r="B1255" t="s">
+      <c r="C1255" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1255" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1255" t="s">
         <v>2614</v>
       </c>
-      <c r="C1255" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1255" t="s">
-        <v>87</v>
-      </c>
-      <c r="E1255" t="s">
-        <v>27</v>
-      </c>
       <c r="F1255" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1256" spans="1:6">
@@ -33349,13 +33355,13 @@
         <v>8</v>
       </c>
       <c r="D1256" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="E1256" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F1256" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1257" spans="1:6">
@@ -33369,13 +33375,13 @@
         <v>8</v>
       </c>
       <c r="D1257" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="E1257" t="s">
         <v>20</v>
       </c>
       <c r="F1257" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1258" spans="1:6">
@@ -33389,41 +33395,41 @@
         <v>8</v>
       </c>
       <c r="D1258" t="s">
-        <v>266</v>
+        <v>87</v>
       </c>
       <c r="E1258" t="s">
-        <v>2621</v>
+        <v>20</v>
       </c>
       <c r="F1258" t="s">
-        <v>267</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1259" spans="1:6">
       <c r="A1259" t="s">
+        <v>2621</v>
+      </c>
+      <c r="B1259" t="s">
         <v>2622</v>
       </c>
-      <c r="B1259" t="s">
+      <c r="C1259" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1259" t="s">
+        <v>266</v>
+      </c>
+      <c r="E1259" t="s">
         <v>2623</v>
       </c>
-      <c r="C1259" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1259" t="s">
-        <v>125</v>
-      </c>
-      <c r="E1259" t="s">
-        <v>2624</v>
-      </c>
       <c r="F1259" t="s">
-        <v>126</v>
+        <v>267</v>
       </c>
     </row>
     <row r="1260" spans="1:6">
       <c r="A1260" t="s">
+        <v>2624</v>
+      </c>
+      <c r="B1260" t="s">
         <v>2625</v>
-      </c>
-      <c r="B1260" t="s">
-        <v>2626</v>
       </c>
       <c r="C1260" t="s">
         <v>8</v>
@@ -33432,7 +33438,7 @@
         <v>125</v>
       </c>
       <c r="E1260" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="F1260" t="s">
         <v>126</v>
@@ -33440,21 +33446,41 @@
     </row>
     <row r="1261" spans="1:6">
       <c r="A1261" t="s">
+        <v>2627</v>
+      </c>
+      <c r="B1261" t="s">
         <v>2628</v>
       </c>
-      <c r="B1261" t="s">
+      <c r="C1261" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1261" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1261" t="s">
         <v>2629</v>
       </c>
-      <c r="C1261" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1261" t="s">
+      <c r="F1261" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:6">
+      <c r="A1262" t="s">
+        <v>2630</v>
+      </c>
+      <c r="B1262" t="s">
+        <v>2631</v>
+      </c>
+      <c r="C1262" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1262" t="s">
         <v>31</v>
       </c>
-      <c r="E1261" t="s">
+      <c r="E1262" t="s">
         <v>431</v>
       </c>
-      <c r="F1261" t="s">
+      <c r="F1262" t="s">
         <v>32</v>
       </c>
     </row>

--- a/api/clv3/xlsx/en/ReportingOrganisation.xlsx
+++ b/api/clv3/xlsx/en/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7572" uniqueCount="2632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7578" uniqueCount="2634">
   <si>
     <t>code</t>
   </si>
@@ -25,15 +25,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:organisation-type-code</t>
+  </si>
+  <si>
+    <t>codeforiati:hq-country-or-region</t>
+  </si>
+  <si>
     <t>codeforiati:organisation-type</t>
   </si>
   <si>
-    <t>codeforiati:hq-country-or-region</t>
-  </si>
-  <si>
-    <t>codeforiati:organisation-type-code</t>
-  </si>
-  <si>
     <t>AU-5</t>
   </si>
   <si>
@@ -43,45 +43,45 @@
     <t>active</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
     <t>Government</t>
   </si>
   <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>44000</t>
   </si>
   <si>
     <t>The World Bank</t>
   </si>
   <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>(No country assigned)</t>
+  </si>
+  <si>
     <t>Multilateral</t>
   </si>
   <si>
-    <t>(No country assigned)</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>US-EIN-941655673</t>
   </si>
   <si>
     <t>The William and Flora Hewlett Foundation</t>
   </si>
   <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
     <t>Foundation</t>
   </si>
   <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>41AAA</t>
   </si>
   <si>
@@ -94,27 +94,27 @@
     <t>Frontline AIDS</t>
   </si>
   <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
     <t>International NGO</t>
   </si>
   <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>XI-IATI-EC_DEVCO</t>
   </si>
   <si>
     <t>European Commission - Directorate-General for International Cooperation and Development</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>Other Public Sector</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>SE-0</t>
   </si>
   <si>
@@ -229,12 +229,12 @@
     <t>Gavi, the vaccine alliance</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>Public Private Partnership</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>US-EIN-300108263</t>
   </si>
   <si>
@@ -277,15 +277,15 @@
     <t>Young Innovations Pvt. Ltd</t>
   </si>
   <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>Nepal</t>
+  </si>
+  <si>
     <t>Academic, Training and Research</t>
   </si>
   <si>
-    <t>Nepal</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
     <t>GB-CHC-327421</t>
   </si>
   <si>
@@ -391,12 +391,12 @@
     <t>ICA:UK</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>National NGO</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>GB-CHC-298316</t>
   </si>
   <si>
@@ -619,15 +619,15 @@
     <t>Southern African Catholic Bishops' Conference Aids Office</t>
   </si>
   <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
     <t>Regional NGO</t>
   </si>
   <si>
-    <t>South Africa</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
     <t>CH-FDJP-CHE-110347351</t>
   </si>
   <si>
@@ -814,12 +814,12 @@
     <t>Triple Line</t>
   </si>
   <si>
+    <t>70</t>
+  </si>
+  <si>
     <t>Private Sector</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>GB-CHC-1058991</t>
   </si>
   <si>
@@ -7871,6 +7871,12 @@
   </si>
   <si>
     <t>United Nations Development Coordination Office</t>
+  </si>
+  <si>
+    <t>GB-COH-02871809</t>
+  </si>
+  <si>
+    <t>Global Witness</t>
   </si>
   <si>
     <t>US-EIN-042103594</t>
@@ -8241,7 +8247,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1262"/>
+  <dimension ref="A1:F1263"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -33395,13 +33401,13 @@
         <v>8</v>
       </c>
       <c r="D1258" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="E1258" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F1258" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1259" spans="1:6">
@@ -33415,41 +33421,41 @@
         <v>8</v>
       </c>
       <c r="D1259" t="s">
-        <v>266</v>
+        <v>87</v>
       </c>
       <c r="E1259" t="s">
-        <v>2623</v>
+        <v>20</v>
       </c>
       <c r="F1259" t="s">
-        <v>267</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1260" spans="1:6">
       <c r="A1260" t="s">
+        <v>2623</v>
+      </c>
+      <c r="B1260" t="s">
         <v>2624</v>
       </c>
-      <c r="B1260" t="s">
+      <c r="C1260" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1260" t="s">
+        <v>266</v>
+      </c>
+      <c r="E1260" t="s">
         <v>2625</v>
       </c>
-      <c r="C1260" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1260" t="s">
-        <v>125</v>
-      </c>
-      <c r="E1260" t="s">
-        <v>2626</v>
-      </c>
       <c r="F1260" t="s">
-        <v>126</v>
+        <v>267</v>
       </c>
     </row>
     <row r="1261" spans="1:6">
       <c r="A1261" t="s">
+        <v>2626</v>
+      </c>
+      <c r="B1261" t="s">
         <v>2627</v>
-      </c>
-      <c r="B1261" t="s">
-        <v>2628</v>
       </c>
       <c r="C1261" t="s">
         <v>8</v>
@@ -33458,7 +33464,7 @@
         <v>125</v>
       </c>
       <c r="E1261" t="s">
-        <v>2629</v>
+        <v>2628</v>
       </c>
       <c r="F1261" t="s">
         <v>126</v>
@@ -33466,21 +33472,41 @@
     </row>
     <row r="1262" spans="1:6">
       <c r="A1262" t="s">
+        <v>2629</v>
+      </c>
+      <c r="B1262" t="s">
         <v>2630</v>
       </c>
-      <c r="B1262" t="s">
+      <c r="C1262" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1262" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1262" t="s">
         <v>2631</v>
       </c>
-      <c r="C1262" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1262" t="s">
+      <c r="F1262" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:6">
+      <c r="A1263" t="s">
+        <v>2632</v>
+      </c>
+      <c r="B1263" t="s">
+        <v>2633</v>
+      </c>
+      <c r="C1263" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1263" t="s">
         <v>31</v>
       </c>
-      <c r="E1262" t="s">
+      <c r="E1263" t="s">
         <v>431</v>
       </c>
-      <c r="F1262" t="s">
+      <c r="F1263" t="s">
         <v>32</v>
       </c>
     </row>

--- a/api/clv3/xlsx/en/ReportingOrganisation.xlsx
+++ b/api/clv3/xlsx/en/ReportingOrganisation.xlsx
@@ -25,12 +25,12 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:organisation-type-code</t>
+  </si>
+  <si>
     <t>codeforiati:organisation-type</t>
   </si>
   <si>
-    <t>codeforiati:organisation-type-code</t>
-  </si>
-  <si>
     <t>codeforiati:hq-country-or-region</t>
   </si>
   <si>
@@ -43,12 +43,12 @@
     <t>active</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>Government</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>Australia</t>
   </si>
   <si>
@@ -58,12 +58,12 @@
     <t>The World Bank</t>
   </si>
   <si>
+    <t>40</t>
+  </si>
+  <si>
     <t>Multilateral</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>(No country assigned)</t>
   </si>
   <si>
@@ -73,12 +73,12 @@
     <t>The William and Flora Hewlett Foundation</t>
   </si>
   <si>
+    <t>60</t>
+  </si>
+  <si>
     <t>Foundation</t>
   </si>
   <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>United States</t>
   </si>
   <si>
@@ -94,12 +94,12 @@
     <t>Frontline AIDS</t>
   </si>
   <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>International NGO</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>United Kingdom</t>
   </si>
   <si>
@@ -109,12 +109,12 @@
     <t>European Commission - Directorate-General for International Cooperation and Development</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>Other Public Sector</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>SE-0</t>
   </si>
   <si>
@@ -229,12 +229,12 @@
     <t>Gavi, the vaccine alliance</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>Public Private Partnership</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>US-EIN-300108263</t>
   </si>
   <si>
@@ -277,12 +277,12 @@
     <t>Young Innovations Pvt. Ltd</t>
   </si>
   <si>
+    <t>80</t>
+  </si>
+  <si>
     <t>Academic, Training and Research</t>
   </si>
   <si>
-    <t>80</t>
-  </si>
-  <si>
     <t>Nepal</t>
   </si>
   <si>
@@ -391,12 +391,12 @@
     <t>ICA:UK</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>National NGO</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>GB-CHC-298316</t>
   </si>
   <si>
@@ -619,12 +619,12 @@
     <t>Southern African Catholic Bishops' Conference Aids Office</t>
   </si>
   <si>
+    <t>23</t>
+  </si>
+  <si>
     <t>Regional NGO</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
     <t>South Africa</t>
   </si>
   <si>
@@ -814,10 +814,10 @@
     <t>Triple Line</t>
   </si>
   <si>
+    <t>70</t>
+  </si>
+  <si>
     <t>Private Sector</t>
-  </si>
-  <si>
-    <t>70</t>
   </si>
   <si>
     <t>GB-CHC-1058991</t>

--- a/api/clv3/xlsx/en/ReportingOrganisation.xlsx
+++ b/api/clv3/xlsx/en/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7608" uniqueCount="2645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7614" uniqueCount="2647">
   <si>
     <t>code</t>
   </si>
@@ -7943,6 +7943,12 @@
   </si>
   <si>
     <t>Brazil</t>
+  </si>
+  <si>
+    <t>NL-KVK-861193660</t>
+  </si>
+  <si>
+    <t>OurLoop Stitchting</t>
   </si>
   <si>
     <t>GB-CHC-1137523</t>
@@ -8280,7 +8286,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1268"/>
+  <dimension ref="A1:F1269"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -33634,12 +33640,32 @@
         <v>8</v>
       </c>
       <c r="D1268" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="E1268" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1268" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:6">
+      <c r="A1269" t="s">
+        <v>2645</v>
+      </c>
+      <c r="B1269" t="s">
+        <v>2646</v>
+      </c>
+      <c r="C1269" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1269" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1269" t="s">
         <v>88</v>
       </c>
-      <c r="F1268" t="s">
+      <c r="F1269" t="s">
         <v>89</v>
       </c>
     </row>

--- a/api/clv3/xlsx/en/ReportingOrganisation.xlsx
+++ b/api/clv3/xlsx/en/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7632" uniqueCount="2653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7638" uniqueCount="2655">
   <si>
     <t>code</t>
   </si>
@@ -7850,6 +7850,12 @@
   </si>
   <si>
     <t>Northern Ireland Cooperation Overseas Ltd</t>
+  </si>
+  <si>
+    <t>NG-CAC-30547</t>
+  </si>
+  <si>
+    <t>Paradigm Initiative</t>
   </si>
   <si>
     <t>JO-MSD-200159274</t>
@@ -8304,7 +8310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1272"/>
+  <dimension ref="A1:F1273"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -33398,13 +33404,13 @@
         <v>8</v>
       </c>
       <c r="D1255" t="s">
-        <v>496</v>
+        <v>345</v>
       </c>
       <c r="E1255" t="s">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="F1255" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1256" spans="1:6">
@@ -33418,13 +33424,13 @@
         <v>8</v>
       </c>
       <c r="D1256" t="s">
-        <v>63</v>
+        <v>496</v>
       </c>
       <c r="E1256" t="s">
-        <v>266</v>
+        <v>125</v>
       </c>
       <c r="F1256" t="s">
-        <v>267</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1257" spans="1:6">
@@ -33438,13 +33444,13 @@
         <v>8</v>
       </c>
       <c r="D1257" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="E1257" t="s">
-        <v>88</v>
+        <v>266</v>
       </c>
       <c r="F1257" t="s">
-        <v>89</v>
+        <v>267</v>
       </c>
     </row>
     <row r="1258" spans="1:6">
@@ -33458,7 +33464,7 @@
         <v>8</v>
       </c>
       <c r="D1258" t="s">
-        <v>431</v>
+        <v>26</v>
       </c>
       <c r="E1258" t="s">
         <v>88</v>
@@ -33478,13 +33484,13 @@
         <v>8</v>
       </c>
       <c r="D1259" t="s">
-        <v>375</v>
+        <v>431</v>
       </c>
       <c r="E1259" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="F1259" t="s">
-        <v>126</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1260" spans="1:6">
@@ -33498,7 +33504,7 @@
         <v>8</v>
       </c>
       <c r="D1260" t="s">
-        <v>2624</v>
+        <v>375</v>
       </c>
       <c r="E1260" t="s">
         <v>125</v>
@@ -33509,22 +33515,22 @@
     </row>
     <row r="1261" spans="1:6">
       <c r="A1261" t="s">
+        <v>2624</v>
+      </c>
+      <c r="B1261" t="s">
         <v>2625</v>
       </c>
-      <c r="B1261" t="s">
+      <c r="C1261" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1261" t="s">
         <v>2626</v>
       </c>
-      <c r="C1261" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1261" t="s">
-        <v>26</v>
-      </c>
       <c r="E1261" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="F1261" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1262" spans="1:6">
@@ -33538,13 +33544,13 @@
         <v>8</v>
       </c>
       <c r="D1262" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E1262" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="F1262" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1263" spans="1:6">
@@ -33558,13 +33564,13 @@
         <v>8</v>
       </c>
       <c r="D1263" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E1263" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F1263" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1264" spans="1:6">
@@ -33578,13 +33584,13 @@
         <v>8</v>
       </c>
       <c r="D1264" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E1264" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="F1264" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1265" spans="1:6">
@@ -33598,47 +33604,47 @@
         <v>8</v>
       </c>
       <c r="D1265" t="s">
-        <v>2635</v>
+        <v>19</v>
       </c>
       <c r="E1265" t="s">
-        <v>266</v>
+        <v>88</v>
       </c>
       <c r="F1265" t="s">
-        <v>267</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1266" spans="1:6">
       <c r="A1266" t="s">
+        <v>2635</v>
+      </c>
+      <c r="B1266" t="s">
         <v>2636</v>
       </c>
-      <c r="B1266" t="s">
+      <c r="C1266" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1266" t="s">
         <v>2637</v>
       </c>
-      <c r="C1266" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1266" t="s">
-        <v>2638</v>
-      </c>
       <c r="E1266" t="s">
-        <v>125</v>
+        <v>266</v>
       </c>
       <c r="F1266" t="s">
-        <v>126</v>
+        <v>267</v>
       </c>
     </row>
     <row r="1267" spans="1:6">
       <c r="A1267" t="s">
+        <v>2638</v>
+      </c>
+      <c r="B1267" t="s">
         <v>2639</v>
       </c>
-      <c r="B1267" t="s">
+      <c r="C1267" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1267" t="s">
         <v>2640</v>
-      </c>
-      <c r="C1267" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1267" t="s">
-        <v>2641</v>
       </c>
       <c r="E1267" t="s">
         <v>125</v>
@@ -33649,22 +33655,22 @@
     </row>
     <row r="1268" spans="1:6">
       <c r="A1268" t="s">
+        <v>2641</v>
+      </c>
+      <c r="B1268" t="s">
         <v>2642</v>
       </c>
-      <c r="B1268" t="s">
+      <c r="C1268" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1268" t="s">
         <v>2643</v>
       </c>
-      <c r="C1268" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1268" t="s">
-        <v>431</v>
-      </c>
       <c r="E1268" t="s">
-        <v>31</v>
+        <v>125</v>
       </c>
       <c r="F1268" t="s">
-        <v>32</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1269" spans="1:6">
@@ -33678,13 +33684,13 @@
         <v>8</v>
       </c>
       <c r="D1269" t="s">
-        <v>26</v>
+        <v>431</v>
       </c>
       <c r="E1269" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F1269" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1270" spans="1:6">
@@ -33698,7 +33704,7 @@
         <v>8</v>
       </c>
       <c r="D1270" t="s">
-        <v>2648</v>
+        <v>26</v>
       </c>
       <c r="E1270" t="s">
         <v>27</v>
@@ -33709,22 +33715,22 @@
     </row>
     <row r="1271" spans="1:6">
       <c r="A1271" t="s">
+        <v>2648</v>
+      </c>
+      <c r="B1271" t="s">
         <v>2649</v>
       </c>
-      <c r="B1271" t="s">
+      <c r="C1271" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1271" t="s">
         <v>2650</v>
       </c>
-      <c r="C1271" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1271" t="s">
-        <v>63</v>
-      </c>
       <c r="E1271" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F1271" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1272" spans="1:6">
@@ -33738,12 +33744,32 @@
         <v>8</v>
       </c>
       <c r="D1272" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="E1272" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1272" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:6">
+      <c r="A1273" t="s">
+        <v>2653</v>
+      </c>
+      <c r="B1273" t="s">
+        <v>2654</v>
+      </c>
+      <c r="C1273" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1273" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1273" t="s">
         <v>88</v>
       </c>
-      <c r="F1272" t="s">
+      <c r="F1273" t="s">
         <v>89</v>
       </c>
     </row>

--- a/api/clv3/xlsx/en/ReportingOrganisation.xlsx
+++ b/api/clv3/xlsx/en/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7650" uniqueCount="2659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7656" uniqueCount="2661">
   <si>
     <t>code</t>
   </si>
@@ -7991,6 +7991,12 @@
   </si>
   <si>
     <t>The Proforest Initiative UK</t>
+  </si>
+  <si>
+    <t>US-EIN-13-4052259</t>
+  </si>
+  <si>
+    <t>Media Development Investment Fund</t>
   </si>
 </sst>
 </file>
@@ -8322,7 +8328,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1275"/>
+  <dimension ref="A1:F1276"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -33825,6 +33831,26 @@
         <v>28</v>
       </c>
     </row>
+    <row r="1276" spans="1:6">
+      <c r="A1276" t="s">
+        <v>2659</v>
+      </c>
+      <c r="B1276" t="s">
+        <v>2660</v>
+      </c>
+      <c r="C1276" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1276" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1276" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1276" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv3/xlsx/en/ReportingOrganisation.xlsx
+++ b/api/clv3/xlsx/en/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7656" uniqueCount="2661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7662" uniqueCount="2663">
   <si>
     <t>code</t>
   </si>
@@ -7991,6 +7991,12 @@
   </si>
   <si>
     <t>The Proforest Initiative UK</t>
+  </si>
+  <si>
+    <t>US-EIN-52-2135531</t>
+  </si>
+  <si>
+    <t>Forest Trends Association</t>
   </si>
   <si>
     <t>US-EIN-13-4052259</t>
@@ -8328,7 +8334,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1276"/>
+  <dimension ref="A1:F1277"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -33851,6 +33857,26 @@
         <v>21</v>
       </c>
     </row>
+    <row r="1277" spans="1:6">
+      <c r="A1277" t="s">
+        <v>2661</v>
+      </c>
+      <c r="B1277" t="s">
+        <v>2662</v>
+      </c>
+      <c r="C1277" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1277" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1277" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1277" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv3/xlsx/en/ReportingOrganisation.xlsx
+++ b/api/clv3/xlsx/en/ReportingOrganisation.xlsx
@@ -28,12 +28,12 @@
     <t>codeforiati:hq-country-or-region</t>
   </si>
   <si>
+    <t>codeforiati:organisation-type</t>
+  </si>
+  <si>
     <t>codeforiati:organisation-type-code</t>
   </si>
   <si>
-    <t>codeforiati:organisation-type</t>
-  </si>
-  <si>
     <t>AU-5</t>
   </si>
   <si>
@@ -46,12 +46,12 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>Government</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
-    <t>Government</t>
-  </si>
-  <si>
     <t>44000</t>
   </si>
   <si>
@@ -61,12 +61,12 @@
     <t>(No country assigned)</t>
   </si>
   <si>
+    <t>Multilateral</t>
+  </si>
+  <si>
     <t>40</t>
   </si>
   <si>
-    <t>Multilateral</t>
-  </si>
-  <si>
     <t>US-EIN-941655673</t>
   </si>
   <si>
@@ -76,12 +76,12 @@
     <t>United States</t>
   </si>
   <si>
+    <t>Foundation</t>
+  </si>
+  <si>
     <t>60</t>
   </si>
   <si>
-    <t>Foundation</t>
-  </si>
-  <si>
     <t>41AAA</t>
   </si>
   <si>
@@ -97,24 +97,24 @@
     <t>United Kingdom</t>
   </si>
   <si>
+    <t>International NGO</t>
+  </si>
+  <si>
     <t>21</t>
   </si>
   <si>
-    <t>International NGO</t>
-  </si>
-  <si>
     <t>XI-IATI-EC_DEVCO</t>
   </si>
   <si>
     <t>European Commission - Directorate-General for International Cooperation and Development</t>
   </si>
   <si>
+    <t>Other Public Sector</t>
+  </si>
+  <si>
     <t>15</t>
   </si>
   <si>
-    <t>Other Public Sector</t>
-  </si>
-  <si>
     <t>SE-0</t>
   </si>
   <si>
@@ -229,12 +229,12 @@
     <t>Gavi, the vaccine alliance</t>
   </si>
   <si>
+    <t>Public Private Partnership</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
-    <t>Public Private Partnership</t>
-  </si>
-  <si>
     <t>US-EIN-300108263</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Nepal</t>
   </si>
   <si>
+    <t>Academic, Training and Research</t>
+  </si>
+  <si>
     <t>80</t>
   </si>
   <si>
-    <t>Academic, Training and Research</t>
-  </si>
-  <si>
     <t>GB-CHC-327421</t>
   </si>
   <si>
@@ -391,12 +391,12 @@
     <t>ICA:UK</t>
   </si>
   <si>
+    <t>National NGO</t>
+  </si>
+  <si>
     <t>22</t>
   </si>
   <si>
-    <t>National NGO</t>
-  </si>
-  <si>
     <t>GB-CHC-298316</t>
   </si>
   <si>
@@ -622,12 +622,12 @@
     <t>South Africa</t>
   </si>
   <si>
+    <t>Regional NGO</t>
+  </si>
+  <si>
     <t>23</t>
   </si>
   <si>
-    <t>Regional NGO</t>
-  </si>
-  <si>
     <t>CH-FDJP-CHE-110347351</t>
   </si>
   <si>
@@ -820,10 +820,10 @@
     <t>Triple Line</t>
   </si>
   <si>
+    <t>Private Sector</t>
+  </si>
+  <si>
     <t>70</t>
-  </si>
-  <si>
-    <t>Private Sector</t>
   </si>
   <si>
     <t>GB-CHC-1058991</t>

--- a/api/clv3/xlsx/en/ReportingOrganisation.xlsx
+++ b/api/clv3/xlsx/en/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7662" uniqueCount="2663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7668" uniqueCount="2665">
   <si>
     <t>code</t>
   </si>
@@ -7997,6 +7997,12 @@
   </si>
   <si>
     <t>Forest Trends Association</t>
+  </si>
+  <si>
+    <t>GB-COH-02515034</t>
+  </si>
+  <si>
+    <t>Timber Trade Federation Ltd.</t>
   </si>
   <si>
     <t>US-EIN-13-4052259</t>
@@ -8334,7 +8340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1277"/>
+  <dimension ref="A1:F1278"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -33868,12 +33874,32 @@
         <v>8</v>
       </c>
       <c r="D1277" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1277" t="s">
+        <v>268</v>
+      </c>
+      <c r="F1277" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:6">
+      <c r="A1278" t="s">
+        <v>2663</v>
+      </c>
+      <c r="B1278" t="s">
+        <v>2664</v>
+      </c>
+      <c r="C1278" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1278" t="s">
         <v>19</v>
       </c>
-      <c r="E1277" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1277" t="s">
+      <c r="E1278" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1278" t="s">
         <v>28</v>
       </c>
     </row>

--- a/api/clv3/xlsx/en/ReportingOrganisation.xlsx
+++ b/api/clv3/xlsx/en/ReportingOrganisation.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:organisation-type</t>
+  </si>
+  <si>
+    <t>codeforiati:hq-country-or-region</t>
+  </si>
+  <si>
+    <t>codeforiati:registry-identifier</t>
+  </si>
+  <si>
     <t>codeforiati:organisation-type-code</t>
   </si>
   <si>
-    <t>codeforiati:hq-country-or-region</t>
-  </si>
-  <si>
-    <t>codeforiati:registry-identifier</t>
-  </si>
-  <si>
-    <t>codeforiati:organisation-type</t>
-  </si>
-  <si>
     <t>AU-5</t>
   </si>
   <si>
@@ -46,54 +46,54 @@
     <t>active</t>
   </si>
   <si>
+    <t>Government</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>ausgov</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>ausgov</t>
-  </si>
-  <si>
-    <t>Government</t>
-  </si>
-  <si>
     <t>44000</t>
   </si>
   <si>
     <t>The World Bank</t>
   </si>
   <si>
+    <t>Multilateral</t>
+  </si>
+  <si>
+    <t>(No country assigned)</t>
+  </si>
+  <si>
+    <t>worldbank</t>
+  </si>
+  <si>
     <t>40</t>
   </si>
   <si>
-    <t>(No country assigned)</t>
-  </si>
-  <si>
-    <t>worldbank</t>
-  </si>
-  <si>
-    <t>Multilateral</t>
-  </si>
-  <si>
     <t>US-EIN-941655673</t>
   </si>
   <si>
     <t>The William and Flora Hewlett Foundation</t>
   </si>
   <si>
+    <t>Foundation</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>hewlett-foundation</t>
+  </si>
+  <si>
     <t>60</t>
   </si>
   <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>hewlett-foundation</t>
-  </si>
-  <si>
-    <t>Foundation</t>
-  </si>
-  <si>
     <t>41AAA</t>
   </si>
   <si>
@@ -109,33 +109,33 @@
     <t>Frontline AIDS</t>
   </si>
   <si>
+    <t>International NGO</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>f-aids</t>
+  </si>
+  <si>
     <t>21</t>
   </si>
   <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>f-aids</t>
-  </si>
-  <si>
-    <t>International NGO</t>
-  </si>
-  <si>
     <t>XI-IATI-EC_DEVCO</t>
   </si>
   <si>
     <t>European Commission - Directorate-General for International Cooperation and Development</t>
   </si>
   <si>
+    <t>Other Public Sector</t>
+  </si>
+  <si>
+    <t>ec-devco</t>
+  </si>
+  <si>
     <t>15</t>
   </si>
   <si>
-    <t>ec-devco</t>
-  </si>
-  <si>
-    <t>Other Public Sector</t>
-  </si>
-  <si>
     <t>SE-0</t>
   </si>
   <si>
@@ -292,15 +292,15 @@
     <t>Gavi, the vaccine alliance</t>
   </si>
   <si>
+    <t>Public Private Partnership</t>
+  </si>
+  <si>
+    <t>gavi</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
-    <t>gavi</t>
-  </si>
-  <si>
-    <t>Public Private Partnership</t>
-  </si>
-  <si>
     <t>US-EIN-300108263</t>
   </si>
   <si>
@@ -361,18 +361,18 @@
     <t>Young Innovations Pvt. Ltd</t>
   </si>
   <si>
+    <t>Academic, Training and Research</t>
+  </si>
+  <si>
+    <t>Nepal</t>
+  </si>
+  <si>
+    <t>yipl</t>
+  </si>
+  <si>
     <t>80</t>
   </si>
   <si>
-    <t>Nepal</t>
-  </si>
-  <si>
-    <t>yipl</t>
-  </si>
-  <si>
-    <t>Academic, Training and Research</t>
-  </si>
-  <si>
     <t>GB-CHC-327421</t>
   </si>
   <si>
@@ -526,15 +526,15 @@
     <t>ICA:UK</t>
   </si>
   <si>
+    <t>National NGO</t>
+  </si>
+  <si>
+    <t>icauk</t>
+  </si>
+  <si>
     <t>22</t>
   </si>
   <si>
-    <t>icauk</t>
-  </si>
-  <si>
-    <t>National NGO</t>
-  </si>
-  <si>
     <t>GB-CHC-298316</t>
   </si>
   <si>
@@ -865,18 +865,18 @@
     <t>Southern African Catholic Bishops' Conference Aids Office</t>
   </si>
   <si>
+    <t>Regional NGO</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
+    <t>sacbc</t>
+  </si>
+  <si>
     <t>23</t>
   </si>
   <si>
-    <t>South Africa</t>
-  </si>
-  <si>
-    <t>sacbc</t>
-  </si>
-  <si>
-    <t>Regional NGO</t>
-  </si>
-  <si>
     <t>CH-FDJP-CHE-110347351</t>
   </si>
   <si>
@@ -1159,13 +1159,13 @@
     <t>Triple Line</t>
   </si>
   <si>
+    <t>Private Sector</t>
+  </si>
+  <si>
+    <t>tripleline_crownagents</t>
+  </si>
+  <si>
     <t>70</t>
-  </si>
-  <si>
-    <t>tripleline_crownagents</t>
-  </si>
-  <si>
-    <t>Private Sector</t>
   </si>
   <si>
     <t>GB-CHC-1058991</t>

--- a/api/clv3/xlsx/en/ReportingOrganisation.xlsx
+++ b/api/clv3/xlsx/en/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14719" uniqueCount="6422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14824" uniqueCount="6469">
   <si>
     <t>code</t>
   </si>
@@ -4744,7 +4744,7 @@
     <t>FR-SIRET-77566669600015</t>
   </si>
   <si>
-    <t>SECOURS CATHOLIQUE - CARITAS FRANCE</t>
+    <t>Secours Catholique - Caritas France</t>
   </si>
   <si>
     <t>sccf</t>
@@ -9331,7 +9331,7 @@
     <t>NL-KVK-27367015</t>
   </si>
   <si>
-    <t>Netherlands Organisation for Scientific Research (NWO)</t>
+    <t>Dutch Research Council (NWO)</t>
   </si>
   <si>
     <t>nwo</t>
@@ -16810,7 +16810,7 @@
     <t>XM-OCHA-HPC6052</t>
   </si>
   <si>
-    <t>Himilo Relief and Development Association (HIRDA)</t>
+    <t>Himilo Relief and Development Association （HIRDA Somalia）</t>
   </si>
   <si>
     <t>hirda</t>
@@ -18685,6 +18685,24 @@
     <t>arin</t>
   </si>
   <si>
+    <t>IN-MHA-231660448</t>
+  </si>
+  <si>
+    <t>CENTRE FOR CHRONIC DISEASE CONTROL</t>
+  </si>
+  <si>
+    <t>ccdc_india</t>
+  </si>
+  <si>
+    <t>TG-NIF-1000047187</t>
+  </si>
+  <si>
+    <t>Women in Law and Development in Africa-Afrique de l’Ouest (WiLDAF-AO)</t>
+  </si>
+  <si>
+    <t>wildafao</t>
+  </si>
+  <si>
     <t>CH-FDJP-CHE365512867</t>
   </si>
   <si>
@@ -18721,6 +18739,84 @@
     <t>adra-sweden</t>
   </si>
   <si>
+    <t>GB-COH-07921860</t>
+  </si>
+  <si>
+    <t>Institutional Investors Group on Climate Change</t>
+  </si>
+  <si>
+    <t>iigcc</t>
+  </si>
+  <si>
+    <t>MZ-MOJ-100493543</t>
+  </si>
+  <si>
+    <t>Associaçao de Protecao do Idosos de Tete</t>
+  </si>
+  <si>
+    <t>apite</t>
+  </si>
+  <si>
+    <t>GB-COH-12075030</t>
+  </si>
+  <si>
+    <t>Impact Knowledge Limited T/A Impact Capital Africa</t>
+  </si>
+  <si>
+    <t>Private Sector in Provider Country</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>ica</t>
+  </si>
+  <si>
+    <t>GB-CHC-1111719</t>
+  </si>
+  <si>
+    <t>Anglo American Foundation</t>
+  </si>
+  <si>
+    <t>aaf</t>
+  </si>
+  <si>
+    <t>TZ-NNCB-00NGO00009862</t>
+  </si>
+  <si>
+    <t>Mtandao wa vikundi vya wakulima na wafugaji Nyancha</t>
+  </si>
+  <si>
+    <t>mviwanya</t>
+  </si>
+  <si>
+    <t>UA-EDR-45583070</t>
+  </si>
+  <si>
+    <t>VRUNA</t>
+  </si>
+  <si>
+    <t>vruna</t>
+  </si>
+  <si>
+    <t>XI-ROR-01ej9dk98</t>
+  </si>
+  <si>
+    <t>University of Melbourne</t>
+  </si>
+  <si>
+    <t>unimelb</t>
+  </si>
+  <si>
+    <t>TH-MOI-KhorThor3005</t>
+  </si>
+  <si>
+    <t>Thai Lawyers for Human Rights</t>
+  </si>
+  <si>
+    <t>tlhr</t>
+  </si>
+  <si>
     <t>SE-ON-252002-6135</t>
   </si>
   <si>
@@ -18782,6 +18878,51 @@
   </si>
   <si>
     <t>pangeaafrica</t>
+  </si>
+  <si>
+    <t>ZA-CIP-2025-956558-08</t>
+  </si>
+  <si>
+    <t>Impact Finance Facility NPC</t>
+  </si>
+  <si>
+    <t>iff-npc</t>
+  </si>
+  <si>
+    <t>ZA-CIT-9063151162</t>
+  </si>
+  <si>
+    <t>University of KwaZulu-Natal</t>
+  </si>
+  <si>
+    <t>ukzn</t>
+  </si>
+  <si>
+    <t>MZ-MOJ-821-B</t>
+  </si>
+  <si>
+    <t>Diocese dos Libombos - ASA</t>
+  </si>
+  <si>
+    <t>asa</t>
+  </si>
+  <si>
+    <t>BR-CNPJ-01567601-0001-43</t>
+  </si>
+  <si>
+    <t>Universidade Federal de Goiás</t>
+  </si>
+  <si>
+    <t>ufg</t>
+  </si>
+  <si>
+    <t>ET-CSA-0067</t>
+  </si>
+  <si>
+    <t>Tesfa Social &amp; Development Association</t>
+  </si>
+  <si>
+    <t>tsda</t>
   </si>
   <si>
     <t>CR-RPJ-3-002-248583</t>
@@ -19611,7 +19752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2111"/>
+  <dimension ref="A1:G2126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -66505,16 +66646,16 @@
         <v>9</v>
       </c>
       <c r="D2045" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2045" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2045" t="s">
         <v>6225</v>
       </c>
       <c r="G2045" t="s">
-        <v>72</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2046" spans="1:7">
@@ -66528,16 +66669,16 @@
         <v>9</v>
       </c>
       <c r="D2046" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E2046" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F2046" t="s">
         <v>6228</v>
       </c>
       <c r="G2046" t="s">
-        <v>436</v>
+        <v>4716</v>
       </c>
     </row>
     <row r="2047" spans="1:7">
@@ -66551,16 +66692,16 @@
         <v>9</v>
       </c>
       <c r="D2047" t="s">
-        <v>175</v>
+        <v>31</v>
       </c>
       <c r="E2047" t="s">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="F2047" t="s">
         <v>6231</v>
       </c>
       <c r="G2047" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2048" spans="1:7">
@@ -66574,16 +66715,16 @@
         <v>9</v>
       </c>
       <c r="D2048" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E2048" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F2048" t="s">
         <v>6234</v>
       </c>
       <c r="G2048" t="s">
-        <v>47</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2049" spans="1:7">
@@ -66597,10 +66738,10 @@
         <v>9</v>
       </c>
       <c r="D2049" t="s">
-        <v>5212</v>
+        <v>175</v>
       </c>
       <c r="E2049" t="s">
-        <v>5213</v>
+        <v>176</v>
       </c>
       <c r="F2049" t="s">
         <v>6237</v>
@@ -66643,10 +66784,10 @@
         <v>9</v>
       </c>
       <c r="D2051" t="s">
-        <v>370</v>
+        <v>37</v>
       </c>
       <c r="E2051" t="s">
-        <v>371</v>
+        <v>38</v>
       </c>
       <c r="F2051" t="s">
         <v>6243</v>
@@ -66666,16 +66807,16 @@
         <v>9</v>
       </c>
       <c r="D2052" t="s">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="E2052" t="s">
-        <v>11</v>
+        <v>176</v>
       </c>
       <c r="F2052" t="s">
         <v>6246</v>
       </c>
       <c r="G2052" t="s">
-        <v>47</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="2053" spans="1:7">
@@ -66689,70 +66830,70 @@
         <v>9</v>
       </c>
       <c r="D2053" t="s">
-        <v>370</v>
+        <v>6249</v>
       </c>
       <c r="E2053" t="s">
-        <v>371</v>
+        <v>6250</v>
       </c>
       <c r="F2053" t="s">
-        <v>6249</v>
+        <v>6251</v>
       </c>
       <c r="G2053" t="s">
-        <v>2421</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2054" spans="1:7">
       <c r="A2054" t="s">
-        <v>6250</v>
+        <v>6252</v>
       </c>
       <c r="B2054" t="s">
-        <v>6251</v>
+        <v>6253</v>
       </c>
       <c r="C2054" t="s">
         <v>9</v>
       </c>
       <c r="D2054" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E2054" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F2054" t="s">
-        <v>6252</v>
+        <v>6254</v>
       </c>
       <c r="G2054" t="s">
-        <v>460</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2055" spans="1:7">
       <c r="A2055" t="s">
-        <v>6253</v>
+        <v>6255</v>
       </c>
       <c r="B2055" t="s">
-        <v>6254</v>
+        <v>6256</v>
       </c>
       <c r="C2055" t="s">
         <v>9</v>
       </c>
       <c r="D2055" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="E2055" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="F2055" t="s">
-        <v>6255</v>
+        <v>6257</v>
       </c>
       <c r="G2055" t="s">
-        <v>705</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2056" spans="1:7">
       <c r="A2056" t="s">
-        <v>6256</v>
+        <v>6258</v>
       </c>
       <c r="B2056" t="s">
-        <v>6257</v>
+        <v>6259</v>
       </c>
       <c r="C2056" t="s">
         <v>9</v>
@@ -66764,93 +66905,99 @@
         <v>176</v>
       </c>
       <c r="F2056" t="s">
-        <v>6258</v>
+        <v>6260</v>
       </c>
       <c r="G2056" t="s">
-        <v>2917</v>
+        <v>927</v>
       </c>
     </row>
     <row r="2057" spans="1:7">
       <c r="A2057" t="s">
-        <v>6259</v>
+        <v>6261</v>
       </c>
       <c r="B2057" t="s">
-        <v>6260</v>
+        <v>6262</v>
       </c>
       <c r="C2057" t="s">
         <v>9</v>
       </c>
+      <c r="D2057" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2057" t="s">
+        <v>371</v>
+      </c>
       <c r="F2057" t="s">
-        <v>6261</v>
+        <v>6263</v>
       </c>
       <c r="G2057" t="s">
-        <v>358</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2058" spans="1:7">
       <c r="A2058" t="s">
-        <v>6262</v>
+        <v>6264</v>
       </c>
       <c r="B2058" t="s">
-        <v>6263</v>
+        <v>6265</v>
       </c>
       <c r="C2058" t="s">
         <v>9</v>
       </c>
       <c r="D2058" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E2058" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F2058" t="s">
-        <v>6264</v>
+        <v>6266</v>
       </c>
       <c r="G2058" t="s">
-        <v>633</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="2059" spans="1:7">
       <c r="A2059" t="s">
-        <v>6265</v>
+        <v>6267</v>
       </c>
       <c r="B2059" t="s">
-        <v>6266</v>
+        <v>6268</v>
       </c>
       <c r="C2059" t="s">
         <v>9</v>
       </c>
       <c r="D2059" t="s">
-        <v>16</v>
+        <v>5212</v>
       </c>
       <c r="E2059" t="s">
-        <v>17</v>
+        <v>5213</v>
       </c>
       <c r="F2059" t="s">
-        <v>6267</v>
+        <v>6269</v>
       </c>
       <c r="G2059" t="s">
-        <v>633</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2060" spans="1:7">
       <c r="A2060" t="s">
-        <v>6268</v>
+        <v>6270</v>
       </c>
       <c r="B2060" t="s">
-        <v>6269</v>
+        <v>6271</v>
       </c>
       <c r="C2060" t="s">
         <v>9</v>
       </c>
       <c r="D2060" t="s">
-        <v>175</v>
+        <v>31</v>
       </c>
       <c r="E2060" t="s">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="F2060" t="s">
-        <v>6270</v>
+        <v>6272</v>
       </c>
       <c r="G2060" t="s">
         <v>47</v>
@@ -66858,45 +67005,45 @@
     </row>
     <row r="2061" spans="1:7">
       <c r="A2061" t="s">
-        <v>6271</v>
+        <v>6273</v>
       </c>
       <c r="B2061" t="s">
-        <v>6272</v>
+        <v>6274</v>
       </c>
       <c r="C2061" t="s">
         <v>9</v>
       </c>
       <c r="D2061" t="s">
-        <v>6029</v>
+        <v>370</v>
       </c>
       <c r="E2061" t="s">
-        <v>6030</v>
+        <v>371</v>
       </c>
       <c r="F2061" t="s">
-        <v>6273</v>
+        <v>6275</v>
       </c>
       <c r="G2061" t="s">
-        <v>436</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2062" spans="1:7">
       <c r="A2062" t="s">
-        <v>6274</v>
+        <v>6276</v>
       </c>
       <c r="B2062" t="s">
-        <v>6275</v>
+        <v>6277</v>
       </c>
       <c r="C2062" t="s">
         <v>9</v>
       </c>
       <c r="D2062" t="s">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="E2062" t="s">
-        <v>176</v>
+        <v>11</v>
       </c>
       <c r="F2062" t="s">
-        <v>6276</v>
+        <v>6278</v>
       </c>
       <c r="G2062" t="s">
         <v>47</v>
@@ -66904,159 +67051,171 @@
     </row>
     <row r="2063" spans="1:7">
       <c r="A2063" t="s">
-        <v>6277</v>
+        <v>6279</v>
       </c>
       <c r="B2063" t="s">
-        <v>6278</v>
+        <v>6280</v>
       </c>
       <c r="C2063" t="s">
         <v>9</v>
       </c>
+      <c r="D2063" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2063" t="s">
+        <v>371</v>
+      </c>
       <c r="F2063" t="s">
-        <v>6279</v>
+        <v>6281</v>
       </c>
       <c r="G2063" t="s">
-        <v>47</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="2064" spans="1:7">
       <c r="A2064" t="s">
-        <v>6280</v>
+        <v>6282</v>
       </c>
       <c r="B2064" t="s">
-        <v>6281</v>
+        <v>6283</v>
       </c>
       <c r="C2064" t="s">
         <v>9</v>
       </c>
       <c r="D2064" t="s">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E2064" t="s">
-        <v>121</v>
+        <v>32</v>
       </c>
       <c r="F2064" t="s">
-        <v>6282</v>
+        <v>6284</v>
       </c>
       <c r="G2064" t="s">
-        <v>4560</v>
+        <v>460</v>
       </c>
     </row>
     <row r="2065" spans="1:7">
       <c r="A2065" t="s">
-        <v>6283</v>
+        <v>6285</v>
       </c>
       <c r="B2065" t="s">
-        <v>6284</v>
+        <v>6286</v>
       </c>
       <c r="C2065" t="s">
         <v>9</v>
       </c>
       <c r="D2065" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="E2065" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="F2065" t="s">
-        <v>6285</v>
+        <v>6287</v>
       </c>
       <c r="G2065" t="s">
-        <v>402</v>
+        <v>705</v>
       </c>
     </row>
     <row r="2066" spans="1:7">
       <c r="A2066" t="s">
-        <v>6286</v>
+        <v>6288</v>
       </c>
       <c r="B2066" t="s">
-        <v>6287</v>
+        <v>6289</v>
       </c>
       <c r="C2066" t="s">
         <v>9</v>
       </c>
       <c r="D2066" t="s">
-        <v>22</v>
+        <v>5212</v>
       </c>
       <c r="E2066" t="s">
-        <v>23</v>
+        <v>5213</v>
       </c>
       <c r="F2066" t="s">
-        <v>6288</v>
+        <v>6290</v>
       </c>
       <c r="G2066" t="s">
-        <v>47</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2067" spans="1:7">
       <c r="A2067" t="s">
-        <v>6289</v>
+        <v>6291</v>
       </c>
       <c r="B2067" t="s">
-        <v>6290</v>
+        <v>6292</v>
       </c>
       <c r="C2067" t="s">
         <v>9</v>
       </c>
       <c r="D2067" t="s">
-        <v>31</v>
+        <v>370</v>
       </c>
       <c r="E2067" t="s">
-        <v>32</v>
+        <v>371</v>
       </c>
       <c r="F2067" t="s">
-        <v>6291</v>
+        <v>6293</v>
       </c>
       <c r="G2067" t="s">
-        <v>481</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2068" spans="1:7">
       <c r="A2068" t="s">
-        <v>6292</v>
+        <v>6294</v>
       </c>
       <c r="B2068" t="s">
-        <v>6293</v>
+        <v>6295</v>
       </c>
       <c r="C2068" t="s">
         <v>9</v>
       </c>
       <c r="D2068" t="s">
-        <v>5212</v>
+        <v>6029</v>
       </c>
       <c r="E2068" t="s">
-        <v>5213</v>
+        <v>6030</v>
       </c>
       <c r="F2068" t="s">
-        <v>6294</v>
+        <v>6296</v>
       </c>
       <c r="G2068" t="s">
-        <v>6295</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="2069" spans="1:7">
       <c r="A2069" t="s">
-        <v>6296</v>
+        <v>6297</v>
       </c>
       <c r="B2069" t="s">
-        <v>6297</v>
+        <v>6298</v>
       </c>
       <c r="C2069" t="s">
         <v>9</v>
       </c>
+      <c r="D2069" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2069" t="s">
+        <v>371</v>
+      </c>
       <c r="F2069" t="s">
-        <v>6298</v>
+        <v>6299</v>
       </c>
       <c r="G2069" t="s">
-        <v>47</v>
+        <v>4359</v>
       </c>
     </row>
     <row r="2070" spans="1:7">
       <c r="A2070" t="s">
-        <v>6299</v>
+        <v>6300</v>
       </c>
       <c r="B2070" t="s">
-        <v>6300</v>
+        <v>6301</v>
       </c>
       <c r="C2070" t="s">
         <v>9</v>
@@ -67068,122 +67227,116 @@
         <v>176</v>
       </c>
       <c r="F2070" t="s">
-        <v>6301</v>
+        <v>6302</v>
       </c>
       <c r="G2070" t="s">
-        <v>683</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="2071" spans="1:7">
       <c r="A2071" t="s">
-        <v>6302</v>
+        <v>6303</v>
       </c>
       <c r="B2071" t="s">
-        <v>6303</v>
+        <v>6304</v>
       </c>
       <c r="C2071" t="s">
         <v>9</v>
       </c>
       <c r="D2071" t="s">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="E2071" t="s">
-        <v>11</v>
+        <v>176</v>
       </c>
       <c r="F2071" t="s">
-        <v>6304</v>
+        <v>6305</v>
       </c>
       <c r="G2071" t="s">
-        <v>503</v>
+        <v>2917</v>
       </c>
     </row>
     <row r="2072" spans="1:7">
       <c r="A2072" t="s">
-        <v>6305</v>
+        <v>6306</v>
       </c>
       <c r="B2072" t="s">
-        <v>4425</v>
+        <v>6307</v>
       </c>
       <c r="C2072" t="s">
         <v>9</v>
       </c>
-      <c r="D2072" t="s">
-        <v>175</v>
-      </c>
-      <c r="E2072" t="s">
-        <v>176</v>
-      </c>
       <c r="F2072" t="s">
-        <v>6306</v>
+        <v>6308</v>
       </c>
       <c r="G2072" t="s">
-        <v>599</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2073" spans="1:7">
       <c r="A2073" t="s">
-        <v>6307</v>
+        <v>6309</v>
       </c>
       <c r="B2073" t="s">
-        <v>6308</v>
+        <v>6310</v>
       </c>
       <c r="C2073" t="s">
         <v>9</v>
       </c>
       <c r="D2073" t="s">
-        <v>175</v>
+        <v>31</v>
       </c>
       <c r="E2073" t="s">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="F2073" t="s">
-        <v>6309</v>
+        <v>6311</v>
       </c>
       <c r="G2073" t="s">
-        <v>436</v>
+        <v>633</v>
       </c>
     </row>
     <row r="2074" spans="1:7">
       <c r="A2074" t="s">
-        <v>6310</v>
+        <v>6312</v>
       </c>
       <c r="B2074" t="s">
-        <v>6311</v>
+        <v>6313</v>
       </c>
       <c r="C2074" t="s">
         <v>9</v>
       </c>
       <c r="D2074" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="E2074" t="s">
-        <v>121</v>
+        <v>17</v>
       </c>
       <c r="F2074" t="s">
-        <v>6312</v>
+        <v>6314</v>
       </c>
       <c r="G2074" t="s">
-        <v>87</v>
+        <v>633</v>
       </c>
     </row>
     <row r="2075" spans="1:7">
       <c r="A2075" t="s">
-        <v>6313</v>
+        <v>6315</v>
       </c>
       <c r="B2075" t="s">
-        <v>6314</v>
+        <v>6316</v>
       </c>
       <c r="C2075" t="s">
         <v>9</v>
       </c>
       <c r="D2075" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2075" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2075" t="s">
-        <v>6315</v>
+        <v>6317</v>
       </c>
       <c r="G2075" t="s">
         <v>47</v>
@@ -67191,33 +67344,33 @@
     </row>
     <row r="2076" spans="1:7">
       <c r="A2076" t="s">
-        <v>6316</v>
+        <v>6318</v>
       </c>
       <c r="B2076" t="s">
-        <v>6317</v>
+        <v>6319</v>
       </c>
       <c r="C2076" t="s">
         <v>9</v>
       </c>
       <c r="D2076" t="s">
-        <v>22</v>
+        <v>6029</v>
       </c>
       <c r="E2076" t="s">
-        <v>23</v>
+        <v>6030</v>
       </c>
       <c r="F2076" t="s">
-        <v>6318</v>
+        <v>6320</v>
       </c>
       <c r="G2076" t="s">
-        <v>47</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2077" spans="1:7">
       <c r="A2077" t="s">
-        <v>6319</v>
+        <v>6321</v>
       </c>
       <c r="B2077" t="s">
-        <v>6320</v>
+        <v>6322</v>
       </c>
       <c r="C2077" t="s">
         <v>9</v>
@@ -67229,156 +67382,156 @@
         <v>176</v>
       </c>
       <c r="F2077" t="s">
-        <v>6321</v>
+        <v>6323</v>
       </c>
       <c r="G2077" t="s">
-        <v>2028</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2078" spans="1:7">
       <c r="A2078" t="s">
-        <v>6322</v>
+        <v>6324</v>
       </c>
       <c r="B2078" t="s">
-        <v>6323</v>
+        <v>6325</v>
       </c>
       <c r="C2078" t="s">
         <v>9</v>
       </c>
-      <c r="D2078" t="s">
-        <v>370</v>
-      </c>
-      <c r="E2078" t="s">
-        <v>371</v>
-      </c>
       <c r="F2078" t="s">
-        <v>6324</v>
+        <v>6326</v>
       </c>
       <c r="G2078" t="s">
-        <v>599</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2079" spans="1:7">
       <c r="A2079" t="s">
-        <v>6325</v>
+        <v>6327</v>
       </c>
       <c r="B2079" t="s">
-        <v>6326</v>
+        <v>6328</v>
       </c>
       <c r="C2079" t="s">
         <v>9</v>
       </c>
       <c r="D2079" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="E2079" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="F2079" t="s">
-        <v>6327</v>
+        <v>6329</v>
       </c>
       <c r="G2079" t="s">
-        <v>1951</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="2080" spans="1:7">
       <c r="A2080" t="s">
-        <v>6328</v>
+        <v>6330</v>
       </c>
       <c r="B2080" t="s">
-        <v>6329</v>
+        <v>6331</v>
       </c>
       <c r="C2080" t="s">
         <v>9</v>
       </c>
+      <c r="D2080" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2080" t="s">
+        <v>176</v>
+      </c>
       <c r="F2080" t="s">
-        <v>6330</v>
+        <v>6332</v>
       </c>
       <c r="G2080" t="s">
-        <v>705</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2081" spans="1:7">
       <c r="A2081" t="s">
-        <v>6331</v>
+        <v>6333</v>
       </c>
       <c r="B2081" t="s">
-        <v>6332</v>
+        <v>6334</v>
       </c>
       <c r="C2081" t="s">
         <v>9</v>
       </c>
       <c r="D2081" t="s">
-        <v>370</v>
+        <v>22</v>
       </c>
       <c r="E2081" t="s">
-        <v>371</v>
+        <v>23</v>
       </c>
       <c r="F2081" t="s">
-        <v>6333</v>
+        <v>6335</v>
       </c>
       <c r="G2081" t="s">
-        <v>470</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2082" spans="1:7">
       <c r="A2082" t="s">
-        <v>6334</v>
+        <v>6336</v>
       </c>
       <c r="B2082" t="s">
-        <v>6335</v>
+        <v>6337</v>
       </c>
       <c r="C2082" t="s">
         <v>9</v>
       </c>
       <c r="D2082" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E2082" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F2082" t="s">
-        <v>6336</v>
+        <v>6338</v>
       </c>
       <c r="G2082" t="s">
-        <v>34</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2083" spans="1:7">
       <c r="A2083" t="s">
-        <v>6337</v>
+        <v>6339</v>
       </c>
       <c r="B2083" t="s">
-        <v>6338</v>
+        <v>6340</v>
       </c>
       <c r="C2083" t="s">
         <v>9</v>
       </c>
       <c r="D2083" t="s">
-        <v>370</v>
+        <v>5212</v>
       </c>
       <c r="E2083" t="s">
-        <v>371</v>
+        <v>5213</v>
       </c>
       <c r="F2083" t="s">
-        <v>6339</v>
+        <v>6341</v>
       </c>
       <c r="G2083" t="s">
-        <v>34</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="2084" spans="1:7">
       <c r="A2084" t="s">
-        <v>6340</v>
+        <v>6343</v>
       </c>
       <c r="B2084" t="s">
-        <v>6341</v>
+        <v>6344</v>
       </c>
       <c r="C2084" t="s">
         <v>9</v>
       </c>
       <c r="F2084" t="s">
-        <v>6342</v>
+        <v>6345</v>
       </c>
       <c r="G2084" t="s">
         <v>47</v>
@@ -67386,10 +67539,10 @@
     </row>
     <row r="2085" spans="1:7">
       <c r="A2085" t="s">
-        <v>6343</v>
+        <v>6346</v>
       </c>
       <c r="B2085" t="s">
-        <v>6344</v>
+        <v>6347</v>
       </c>
       <c r="C2085" t="s">
         <v>9</v>
@@ -67401,41 +67554,41 @@
         <v>176</v>
       </c>
       <c r="F2085" t="s">
-        <v>6345</v>
+        <v>6348</v>
       </c>
       <c r="G2085" t="s">
-        <v>2533</v>
+        <v>683</v>
       </c>
     </row>
     <row r="2086" spans="1:7">
       <c r="A2086" t="s">
-        <v>6346</v>
+        <v>6349</v>
       </c>
       <c r="B2086" t="s">
-        <v>6347</v>
+        <v>6350</v>
       </c>
       <c r="C2086" t="s">
         <v>9</v>
       </c>
       <c r="D2086" t="s">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="E2086" t="s">
-        <v>176</v>
+        <v>11</v>
       </c>
       <c r="F2086" t="s">
-        <v>6348</v>
+        <v>6351</v>
       </c>
       <c r="G2086" t="s">
-        <v>47</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2087" spans="1:7">
       <c r="A2087" t="s">
-        <v>6349</v>
+        <v>6352</v>
       </c>
       <c r="B2087" t="s">
-        <v>6350</v>
+        <v>4425</v>
       </c>
       <c r="C2087" t="s">
         <v>9</v>
@@ -67447,150 +67600,156 @@
         <v>176</v>
       </c>
       <c r="F2087" t="s">
-        <v>6351</v>
+        <v>6353</v>
       </c>
       <c r="G2087" t="s">
-        <v>47</v>
+        <v>599</v>
       </c>
     </row>
     <row r="2088" spans="1:7">
       <c r="A2088" t="s">
-        <v>6352</v>
+        <v>6354</v>
       </c>
       <c r="B2088" t="s">
-        <v>6353</v>
+        <v>6355</v>
       </c>
       <c r="C2088" t="s">
         <v>9</v>
       </c>
       <c r="D2088" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2088" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2088" t="s">
-        <v>6354</v>
+        <v>6356</v>
       </c>
       <c r="G2088" t="s">
-        <v>47</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2089" spans="1:7">
       <c r="A2089" t="s">
-        <v>6355</v>
+        <v>6357</v>
       </c>
       <c r="B2089" t="s">
-        <v>6356</v>
+        <v>6358</v>
       </c>
       <c r="C2089" t="s">
         <v>9</v>
       </c>
       <c r="D2089" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="E2089" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="F2089" t="s">
-        <v>6357</v>
+        <v>6359</v>
       </c>
       <c r="G2089" t="s">
-        <v>927</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2090" spans="1:7">
       <c r="A2090" t="s">
-        <v>6358</v>
+        <v>6360</v>
       </c>
       <c r="B2090" t="s">
-        <v>6359</v>
+        <v>6361</v>
       </c>
       <c r="C2090" t="s">
         <v>9</v>
       </c>
+      <c r="D2090" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2090" t="s">
+        <v>32</v>
+      </c>
       <c r="F2090" t="s">
-        <v>6360</v>
+        <v>6362</v>
       </c>
       <c r="G2090" t="s">
-        <v>436</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2091" spans="1:7">
       <c r="A2091" t="s">
-        <v>6361</v>
+        <v>6363</v>
       </c>
       <c r="B2091" t="s">
-        <v>6362</v>
+        <v>6364</v>
       </c>
       <c r="C2091" t="s">
         <v>9</v>
       </c>
       <c r="D2091" t="s">
-        <v>370</v>
+        <v>22</v>
       </c>
       <c r="E2091" t="s">
-        <v>371</v>
+        <v>23</v>
       </c>
       <c r="F2091" t="s">
-        <v>6363</v>
+        <v>6365</v>
       </c>
       <c r="G2091" t="s">
-        <v>3677</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2092" spans="1:7">
       <c r="A2092" t="s">
-        <v>6364</v>
+        <v>6366</v>
       </c>
       <c r="B2092" t="s">
-        <v>6365</v>
+        <v>6367</v>
       </c>
       <c r="C2092" t="s">
         <v>9</v>
       </c>
       <c r="D2092" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2092" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2092" t="s">
-        <v>6366</v>
+        <v>6368</v>
       </c>
       <c r="G2092" t="s">
-        <v>25</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="2093" spans="1:7">
       <c r="A2093" t="s">
-        <v>6367</v>
+        <v>6369</v>
       </c>
       <c r="B2093" t="s">
-        <v>6368</v>
+        <v>6370</v>
       </c>
       <c r="C2093" t="s">
         <v>9</v>
       </c>
       <c r="D2093" t="s">
-        <v>175</v>
+        <v>370</v>
       </c>
       <c r="E2093" t="s">
-        <v>176</v>
+        <v>371</v>
       </c>
       <c r="F2093" t="s">
-        <v>6369</v>
+        <v>6371</v>
       </c>
       <c r="G2093" t="s">
-        <v>1935</v>
+        <v>599</v>
       </c>
     </row>
     <row r="2094" spans="1:7">
       <c r="A2094" t="s">
-        <v>6370</v>
+        <v>6372</v>
       </c>
       <c r="B2094" t="s">
-        <v>6371</v>
+        <v>6373</v>
       </c>
       <c r="C2094" t="s">
         <v>9</v>
@@ -67602,139 +67761,133 @@
         <v>176</v>
       </c>
       <c r="F2094" t="s">
-        <v>6372</v>
+        <v>6374</v>
       </c>
       <c r="G2094" t="s">
-        <v>6295</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="2095" spans="1:7">
       <c r="A2095" t="s">
-        <v>6373</v>
+        <v>6375</v>
       </c>
       <c r="B2095" t="s">
-        <v>6374</v>
+        <v>6376</v>
       </c>
       <c r="C2095" t="s">
         <v>9</v>
       </c>
-      <c r="D2095" t="s">
-        <v>175</v>
-      </c>
-      <c r="E2095" t="s">
-        <v>176</v>
-      </c>
       <c r="F2095" t="s">
-        <v>6375</v>
+        <v>6377</v>
       </c>
       <c r="G2095" t="s">
-        <v>6204</v>
+        <v>705</v>
       </c>
     </row>
     <row r="2096" spans="1:7">
       <c r="A2096" t="s">
-        <v>6376</v>
+        <v>6378</v>
       </c>
       <c r="B2096" t="s">
-        <v>6377</v>
+        <v>6379</v>
       </c>
       <c r="C2096" t="s">
         <v>9</v>
       </c>
+      <c r="D2096" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2096" t="s">
+        <v>371</v>
+      </c>
       <c r="F2096" t="s">
-        <v>6378</v>
+        <v>6380</v>
       </c>
       <c r="G2096" t="s">
-        <v>47</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2097" spans="1:7">
       <c r="A2097" t="s">
-        <v>6379</v>
+        <v>6381</v>
       </c>
       <c r="B2097" t="s">
-        <v>6380</v>
+        <v>6382</v>
       </c>
       <c r="C2097" t="s">
         <v>9</v>
       </c>
       <c r="D2097" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="E2097" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="F2097" t="s">
-        <v>6381</v>
+        <v>6383</v>
       </c>
       <c r="G2097" t="s">
-        <v>358</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2098" spans="1:7">
       <c r="A2098" t="s">
-        <v>6382</v>
+        <v>6384</v>
       </c>
       <c r="B2098" t="s">
-        <v>6383</v>
+        <v>6385</v>
       </c>
       <c r="C2098" t="s">
         <v>9</v>
       </c>
       <c r="D2098" t="s">
-        <v>175</v>
+        <v>370</v>
       </c>
       <c r="E2098" t="s">
-        <v>176</v>
+        <v>371</v>
       </c>
       <c r="F2098" t="s">
-        <v>6384</v>
+        <v>6386</v>
       </c>
       <c r="G2098" t="s">
-        <v>927</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2099" spans="1:7">
       <c r="A2099" t="s">
-        <v>6385</v>
+        <v>6387</v>
       </c>
       <c r="B2099" t="s">
-        <v>6386</v>
+        <v>6388</v>
       </c>
       <c r="C2099" t="s">
         <v>9</v>
       </c>
-      <c r="D2099" t="s">
-        <v>370</v>
-      </c>
-      <c r="E2099" t="s">
-        <v>371</v>
-      </c>
       <c r="F2099" t="s">
-        <v>6387</v>
+        <v>6389</v>
       </c>
       <c r="G2099" t="s">
-        <v>1706</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2100" spans="1:7">
       <c r="A2100" t="s">
-        <v>6388</v>
+        <v>6390</v>
       </c>
       <c r="B2100" t="s">
-        <v>6389</v>
+        <v>6391</v>
       </c>
       <c r="C2100" t="s">
         <v>9</v>
       </c>
       <c r="D2100" t="s">
-        <v>22</v>
+        <v>175</v>
       </c>
       <c r="E2100" t="s">
-        <v>23</v>
+        <v>176</v>
       </c>
       <c r="F2100" t="s">
-        <v>6390</v>
+        <v>6392</v>
       </c>
       <c r="G2100" t="s">
         <v>2533</v>
@@ -67742,10 +67895,10 @@
     </row>
     <row r="2101" spans="1:7">
       <c r="A2101" t="s">
-        <v>6391</v>
+        <v>6393</v>
       </c>
       <c r="B2101" t="s">
-        <v>6392</v>
+        <v>6394</v>
       </c>
       <c r="C2101" t="s">
         <v>9</v>
@@ -67757,41 +67910,41 @@
         <v>176</v>
       </c>
       <c r="F2101" t="s">
-        <v>6393</v>
+        <v>6395</v>
       </c>
       <c r="G2101" t="s">
-        <v>2837</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2102" spans="1:7">
       <c r="A2102" t="s">
-        <v>6394</v>
+        <v>6396</v>
       </c>
       <c r="B2102" t="s">
-        <v>6395</v>
+        <v>6397</v>
       </c>
       <c r="C2102" t="s">
         <v>9</v>
       </c>
       <c r="D2102" t="s">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="E2102" t="s">
-        <v>11</v>
+        <v>176</v>
       </c>
       <c r="F2102" t="s">
-        <v>6396</v>
+        <v>6398</v>
       </c>
       <c r="G2102" t="s">
-        <v>5837</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2103" spans="1:7">
       <c r="A2103" t="s">
-        <v>6397</v>
+        <v>6399</v>
       </c>
       <c r="B2103" t="s">
-        <v>6398</v>
+        <v>6400</v>
       </c>
       <c r="C2103" t="s">
         <v>9</v>
@@ -67803,7 +67956,7 @@
         <v>32</v>
       </c>
       <c r="F2103" t="s">
-        <v>6399</v>
+        <v>6401</v>
       </c>
       <c r="G2103" t="s">
         <v>47</v>
@@ -67811,102 +67964,96 @@
     </row>
     <row r="2104" spans="1:7">
       <c r="A2104" t="s">
-        <v>6400</v>
+        <v>6402</v>
       </c>
       <c r="B2104" t="s">
-        <v>6401</v>
+        <v>6403</v>
       </c>
       <c r="C2104" t="s">
         <v>9</v>
       </c>
       <c r="D2104" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2104" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2104" t="s">
-        <v>6402</v>
+        <v>6404</v>
       </c>
       <c r="G2104" t="s">
-        <v>47</v>
+        <v>927</v>
       </c>
     </row>
     <row r="2105" spans="1:7">
       <c r="A2105" t="s">
-        <v>6403</v>
+        <v>6405</v>
       </c>
       <c r="B2105" t="s">
-        <v>6404</v>
+        <v>6406</v>
       </c>
       <c r="C2105" t="s">
         <v>9</v>
       </c>
-      <c r="D2105" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2105" t="s">
-        <v>32</v>
-      </c>
       <c r="F2105" t="s">
-        <v>6405</v>
+        <v>6407</v>
       </c>
       <c r="G2105" t="s">
-        <v>47</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2106" spans="1:7">
       <c r="A2106" t="s">
-        <v>6406</v>
+        <v>6408</v>
       </c>
       <c r="B2106" t="s">
-        <v>6407</v>
+        <v>6409</v>
       </c>
       <c r="C2106" t="s">
         <v>9</v>
       </c>
       <c r="D2106" t="s">
-        <v>22</v>
+        <v>370</v>
       </c>
       <c r="E2106" t="s">
-        <v>23</v>
+        <v>371</v>
       </c>
       <c r="F2106" t="s">
-        <v>6408</v>
+        <v>6410</v>
       </c>
       <c r="G2106" t="s">
-        <v>47</v>
+        <v>3677</v>
       </c>
     </row>
     <row r="2107" spans="1:7">
       <c r="A2107" t="s">
-        <v>6409</v>
+        <v>6411</v>
       </c>
       <c r="B2107" t="s">
-        <v>6410</v>
+        <v>6412</v>
       </c>
       <c r="C2107" t="s">
         <v>9</v>
       </c>
       <c r="D2107" t="s">
-        <v>290</v>
+        <v>31</v>
       </c>
       <c r="E2107" t="s">
-        <v>291</v>
+        <v>32</v>
       </c>
       <c r="F2107" t="s">
-        <v>6411</v>
+        <v>6413</v>
       </c>
       <c r="G2107" t="s">
-        <v>436</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2108" spans="1:7">
       <c r="A2108" t="s">
-        <v>6412</v>
+        <v>6414</v>
       </c>
       <c r="B2108" t="s">
-        <v>6413</v>
+        <v>6415</v>
       </c>
       <c r="C2108" t="s">
         <v>9</v>
@@ -67918,78 +68065,417 @@
         <v>176</v>
       </c>
       <c r="F2108" t="s">
-        <v>6414</v>
+        <v>6416</v>
       </c>
       <c r="G2108" t="s">
-        <v>358</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="2109" spans="1:7">
       <c r="A2109" t="s">
-        <v>6415</v>
+        <v>6417</v>
       </c>
       <c r="B2109" t="s">
-        <v>6416</v>
+        <v>6418</v>
       </c>
       <c r="C2109" t="s">
         <v>9</v>
       </c>
       <c r="D2109" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2109" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2109" t="s">
-        <v>6417</v>
+        <v>6419</v>
       </c>
       <c r="G2109" t="s">
-        <v>47</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="2110" spans="1:7">
       <c r="A2110" t="s">
-        <v>6418</v>
+        <v>6420</v>
       </c>
       <c r="B2110" t="s">
-        <v>5025</v>
+        <v>6421</v>
       </c>
       <c r="C2110" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D2110" t="s">
-        <v>290</v>
+        <v>175</v>
       </c>
       <c r="E2110" t="s">
-        <v>291</v>
+        <v>176</v>
       </c>
       <c r="F2110" t="s">
-        <v>5026</v>
+        <v>6422</v>
       </c>
       <c r="G2110" t="s">
-        <v>1706</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="2111" spans="1:7">
       <c r="A2111" t="s">
-        <v>6419</v>
+        <v>6423</v>
       </c>
       <c r="B2111" t="s">
-        <v>6420</v>
+        <v>6424</v>
       </c>
       <c r="C2111" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2111" t="s">
+        <v>6425</v>
+      </c>
+      <c r="G2111" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:7">
+      <c r="A2112" t="s">
+        <v>6426</v>
+      </c>
+      <c r="B2112" t="s">
+        <v>6427</v>
+      </c>
+      <c r="C2112" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2112" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2112" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2112" t="s">
+        <v>6428</v>
+      </c>
+      <c r="G2112" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:7">
+      <c r="A2113" t="s">
+        <v>6429</v>
+      </c>
+      <c r="B2113" t="s">
+        <v>6430</v>
+      </c>
+      <c r="C2113" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2113" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2113" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2113" t="s">
+        <v>6431</v>
+      </c>
+      <c r="G2113" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:7">
+      <c r="A2114" t="s">
+        <v>6432</v>
+      </c>
+      <c r="B2114" t="s">
+        <v>6433</v>
+      </c>
+      <c r="C2114" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2114" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2114" t="s">
+        <v>371</v>
+      </c>
+      <c r="F2114" t="s">
+        <v>6434</v>
+      </c>
+      <c r="G2114" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:7">
+      <c r="A2115" t="s">
+        <v>6435</v>
+      </c>
+      <c r="B2115" t="s">
+        <v>6436</v>
+      </c>
+      <c r="C2115" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2115" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2115" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2115" t="s">
+        <v>6437</v>
+      </c>
+      <c r="G2115" t="s">
+        <v>2533</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:7">
+      <c r="A2116" t="s">
+        <v>6438</v>
+      </c>
+      <c r="B2116" t="s">
+        <v>6439</v>
+      </c>
+      <c r="C2116" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2116" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2116" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2116" t="s">
+        <v>6440</v>
+      </c>
+      <c r="G2116" t="s">
+        <v>2837</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:7">
+      <c r="A2117" t="s">
+        <v>6441</v>
+      </c>
+      <c r="B2117" t="s">
+        <v>6442</v>
+      </c>
+      <c r="C2117" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2117" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2117" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2117" t="s">
+        <v>6443</v>
+      </c>
+      <c r="G2117" t="s">
+        <v>5837</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:7">
+      <c r="A2118" t="s">
+        <v>6444</v>
+      </c>
+      <c r="B2118" t="s">
+        <v>6445</v>
+      </c>
+      <c r="C2118" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2118" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2118" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2118" t="s">
+        <v>6446</v>
+      </c>
+      <c r="G2118" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:7">
+      <c r="A2119" t="s">
+        <v>6447</v>
+      </c>
+      <c r="B2119" t="s">
+        <v>6448</v>
+      </c>
+      <c r="C2119" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2119" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2119" t="s">
+        <v>6449</v>
+      </c>
+      <c r="G2119" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:7">
+      <c r="A2120" t="s">
+        <v>6450</v>
+      </c>
+      <c r="B2120" t="s">
+        <v>6451</v>
+      </c>
+      <c r="C2120" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2120" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2120" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2120" t="s">
+        <v>6452</v>
+      </c>
+      <c r="G2120" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:7">
+      <c r="A2121" t="s">
+        <v>6453</v>
+      </c>
+      <c r="B2121" t="s">
+        <v>6454</v>
+      </c>
+      <c r="C2121" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2121" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2121" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2121" t="s">
+        <v>6455</v>
+      </c>
+      <c r="G2121" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:7">
+      <c r="A2122" t="s">
+        <v>6456</v>
+      </c>
+      <c r="B2122" t="s">
+        <v>6457</v>
+      </c>
+      <c r="C2122" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2122" t="s">
+        <v>290</v>
+      </c>
+      <c r="E2122" t="s">
+        <v>291</v>
+      </c>
+      <c r="F2122" t="s">
+        <v>6458</v>
+      </c>
+      <c r="G2122" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:7">
+      <c r="A2123" t="s">
+        <v>6459</v>
+      </c>
+      <c r="B2123" t="s">
+        <v>6460</v>
+      </c>
+      <c r="C2123" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2123" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2123" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2123" t="s">
+        <v>6461</v>
+      </c>
+      <c r="G2123" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:7">
+      <c r="A2124" t="s">
+        <v>6462</v>
+      </c>
+      <c r="B2124" t="s">
+        <v>6463</v>
+      </c>
+      <c r="C2124" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2124" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2124" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2124" t="s">
+        <v>6464</v>
+      </c>
+      <c r="G2124" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:7">
+      <c r="A2125" t="s">
+        <v>6465</v>
+      </c>
+      <c r="B2125" t="s">
+        <v>5025</v>
+      </c>
+      <c r="C2125" t="s">
         <v>42</v>
       </c>
-      <c r="D2111" t="s">
+      <c r="D2125" t="s">
+        <v>290</v>
+      </c>
+      <c r="E2125" t="s">
+        <v>291</v>
+      </c>
+      <c r="F2125" t="s">
+        <v>5026</v>
+      </c>
+      <c r="G2125" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:7">
+      <c r="A2126" t="s">
+        <v>6466</v>
+      </c>
+      <c r="B2126" t="s">
+        <v>6467</v>
+      </c>
+      <c r="C2126" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2126" t="s">
         <v>370</v>
       </c>
-      <c r="E2111" t="s">
+      <c r="E2126" t="s">
         <v>371</v>
       </c>
-      <c r="F2111" t="s">
-        <v>6421</v>
-      </c>
-      <c r="G2111" t="s">
+      <c r="F2126" t="s">
+        <v>6468</v>
+      </c>
+      <c r="G2126" t="s">
         <v>524</v>
       </c>
     </row>
